--- a/results_cnn_subnetwork_evaluation/summary.xlsx
+++ b/results_cnn_subnetwork_evaluation/summary.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_enhancement_dm\results_cnn_subnetwork_evaluation\PG-AC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_cnn_subnetwork_evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AA8A4C8-8362-4732-9E03-989F9263F649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79444A4C-DC24-4D7F-B2FA-836CDD642F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fullldata_20260110" sheetId="5" r:id="rId1"/>
@@ -433,36 +433,36 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -814,10 +814,10 @@
       <c r="V1" s="27"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="52" t="s">
+      <c r="A2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="53"/>
+      <c r="B2" s="51"/>
       <c r="C2" s="28">
         <v>93.101364775358491</v>
       </c>
@@ -851,10 +851,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="52" t="s">
+      <c r="M2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="53"/>
+      <c r="N2" s="51"/>
       <c r="O2" s="32">
         <v>3.4649270444699574</v>
       </c>
@@ -882,10 +882,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
+      <c r="A3" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="53"/>
+      <c r="B3" s="51"/>
       <c r="C3" s="32">
         <v>93.273358766079312</v>
       </c>
@@ -919,10 +919,10 @@
         <f t="shared" ref="L3:L8" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="52" t="s">
+      <c r="M3" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="53"/>
+      <c r="N3" s="51"/>
       <c r="O3" s="32">
         <v>3.4672469457762647</v>
       </c>
@@ -1022,10 +1022,10 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52" t="s">
+      <c r="A5" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="53"/>
+      <c r="B5" s="51"/>
       <c r="C5" s="42">
         <v>93.32548436116808</v>
       </c>
@@ -1059,10 +1059,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.3254843611681, 92.7395392693709, 91.5008722682146, 85.1433691756272, 75.1472994287724, 59.1298425303564, 48.3641900016436,</v>
       </c>
-      <c r="M5" s="52" t="s">
+      <c r="M5" s="50" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="53"/>
+      <c r="N5" s="51"/>
       <c r="O5" s="42">
         <v>3.667959563183556</v>
       </c>
@@ -1090,10 +1090,10 @@
       </c>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="56"/>
+      <c r="B6" s="54"/>
       <c r="C6" s="42">
         <v>93.029579263949799</v>
       </c>
@@ -1127,10 +1127,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    93.0295792639498, 91.6994899033152, 90.2301029132316, 85.6844378699931, 76.6044083426327, 60.5252409911274, 50.5464637814053,</v>
       </c>
-      <c r="M6" s="52" t="s">
+      <c r="M6" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="53"/>
+      <c r="N6" s="51"/>
       <c r="O6" s="42">
         <v>3.744976414623296</v>
       </c>
@@ -1161,7 +1161,7 @@
       <c r="A7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="54" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="32">
@@ -1200,7 +1200,7 @@
       <c r="M7" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="N7" s="56" t="s">
+      <c r="N7" s="54" t="s">
         <v>12</v>
       </c>
       <c r="O7" s="38">
@@ -1233,7 +1233,7 @@
       <c r="A8" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="57"/>
+      <c r="B8" s="55"/>
       <c r="C8" s="35">
         <v>92.961657684466715</v>
       </c>
@@ -1270,7 +1270,7 @@
       <c r="M8" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="N8" s="57"/>
+      <c r="N8" s="55"/>
       <c r="O8" s="35">
         <v>3.561541743303076</v>
       </c>
@@ -1359,10 +1359,10 @@
       <c r="V10" s="20"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="54" t="s">
+      <c r="A11" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="55"/>
+      <c r="B11" s="53"/>
       <c r="C11" s="21">
         <v>92.567111769713335</v>
       </c>
@@ -1390,10 +1390,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C11:I11)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M11" s="54" t="s">
+      <c r="M11" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="N11" s="55"/>
+      <c r="N11" s="53"/>
       <c r="O11" s="23">
         <v>3.88093621561358</v>
       </c>
@@ -1421,10 +1421,10 @@
       </c>
     </row>
     <row r="12" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="55"/>
+      <c r="B12" s="53"/>
       <c r="C12" s="21">
         <v>92.866950218042462</v>
       </c>
@@ -1452,10 +1452,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C12:I12)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M12" s="54" t="s">
+      <c r="M12" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="N12" s="55"/>
+      <c r="N12" s="53"/>
       <c r="O12" s="21">
         <v>3.8319643020864191</v>
       </c>
@@ -1549,10 +1549,10 @@
       </c>
     </row>
     <row r="14" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="54" t="s">
+      <c r="A14" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="55"/>
+      <c r="B14" s="53"/>
       <c r="C14" s="45">
         <v>92.868050634154315</v>
       </c>
@@ -1580,10 +1580,10 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve">    92.8680506341543, 92.2882312220453, 91.0542871480351, 84.4378853330854, 74.2536733835995, 57.5521955589916, 45.5609776547364,</v>
       </c>
-      <c r="M14" s="54" t="s">
+      <c r="M14" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="N14" s="55"/>
+      <c r="N14" s="53"/>
       <c r="O14" s="45">
         <v>4.0949495507503526</v>
       </c>
@@ -1611,10 +1611,10 @@
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="54" t="s">
+      <c r="A15" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="55"/>
+      <c r="B15" s="53"/>
       <c r="C15" s="45">
         <v>92.513598322189821</v>
       </c>
@@ -1642,10 +1642,10 @@
         <f t="shared" si="3"/>
         <v xml:space="preserve">    92.5135983221898, 91.2614468705945, 89.7582659416619, 85.0444656561297, 75.8988439680803, 59.4656118371167, 48.4731564902542,</v>
       </c>
-      <c r="M15" s="54" t="s">
+      <c r="M15" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="55"/>
+      <c r="N15" s="53"/>
       <c r="O15" s="45">
         <v>4.2171731523020446</v>
       </c>
@@ -1676,7 +1676,7 @@
       <c r="A16" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="57" t="s">
         <v>12</v>
       </c>
       <c r="C16" s="40">
@@ -1709,7 +1709,7 @@
       <c r="M16" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="N16" s="50" t="s">
+      <c r="N16" s="57" t="s">
         <v>12</v>
       </c>
       <c r="O16" s="40">
@@ -1742,7 +1742,7 @@
       <c r="A17" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="51"/>
+      <c r="B17" s="58"/>
       <c r="C17" s="24">
         <v>92.570176373736686</v>
       </c>
@@ -1773,7 +1773,7 @@
       <c r="M17" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="N17" s="51"/>
+      <c r="N17" s="58"/>
       <c r="O17" s="24">
         <v>3.882028195540002</v>
       </c>
@@ -1855,6 +1855,13 @@
       <c r="U21" s="2"/>
     </row>
     <row r="22" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="I22"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
@@ -1867,6 +1874,7 @@
       <c r="U22" s="2"/>
     </row>
     <row r="23" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+      <c r="C23"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -1891,6 +1899,7 @@
       <c r="U24" s="2"/>
     </row>
     <row r="25" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+      <c r="C25"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -1915,6 +1924,7 @@
       <c r="U26" s="2"/>
     </row>
     <row r="27" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+      <c r="C27"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -1927,7 +1937,6 @@
       <c r="U27" s="2"/>
     </row>
     <row r="28" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
@@ -1948,7 +1957,7 @@
       <c r="U28" s="2"/>
     </row>
     <row r="29" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="C29" s="2"/>
+      <c r="C29"/>
       <c r="D29" s="2"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
@@ -1969,7 +1978,6 @@
       <c r="U29" s="2"/>
     </row>
     <row r="30" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="C30" s="2"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -1990,7 +1998,7 @@
       <c r="U30" s="2"/>
     </row>
     <row r="31" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="C31" s="2"/>
+      <c r="C31"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -2011,7 +2019,6 @@
       <c r="U31" s="2"/>
     </row>
     <row r="32" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="C32" s="2"/>
       <c r="D32" s="2"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
@@ -2032,7 +2039,7 @@
       <c r="U32" s="2"/>
     </row>
     <row r="33" spans="3:21" ht="15" x14ac:dyDescent="0.2">
-      <c r="C33" s="2"/>
+      <c r="C33"/>
       <c r="D33" s="2"/>
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
@@ -2053,7 +2060,6 @@
       <c r="U33" s="2"/>
     </row>
     <row r="34" spans="3:21" ht="15" x14ac:dyDescent="0.2">
-      <c r="C34" s="2"/>
       <c r="D34" s="2"/>
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
@@ -2074,7 +2080,7 @@
       <c r="U34" s="2"/>
     </row>
     <row r="35" spans="3:21" ht="15" x14ac:dyDescent="0.2">
-      <c r="C35" s="2"/>
+      <c r="C35"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
@@ -2243,6 +2249,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="N16:N17"/>
+    <mergeCell ref="M5:N5"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="M12:N12"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="A11:B11"/>
@@ -2253,16 +2269,6 @@
     <mergeCell ref="M3:N3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="N16:N17"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="M12:N12"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:I8">

--- a/results_cnn_subnetwork_evaluation/summary.xlsx
+++ b/results_cnn_subnetwork_evaluation/summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_cnn_subnetwork_evaluation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_cnn_subnetwork_evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79444A4C-DC24-4D7F-B2FA-836CDD642F4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{105469B6-EFE3-46A9-BCFC-A8A9C02C04A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fullldata_20260110" sheetId="5" r:id="rId1"/>
@@ -338,7 +338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -460,9 +460,10 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1803,9 +1804,9 @@
     <row r="19" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
+      <c r="E19"/>
+      <c r="F19"/>
+      <c r="G19"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
@@ -1855,11 +1856,9 @@
       <c r="U21" s="2"/>
     </row>
     <row r="22" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
       <c r="H22"/>
       <c r="I22"/>
       <c r="L22" s="2"/>
@@ -1874,7 +1873,7 @@
       <c r="U22" s="2"/>
     </row>
     <row r="23" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="C23"/>
+      <c r="C23" s="59"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -1887,6 +1886,7 @@
       <c r="U23" s="2"/>
     </row>
     <row r="24" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+      <c r="D24"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -1899,7 +1899,7 @@
       <c r="U24" s="2"/>
     </row>
     <row r="25" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="C25"/>
+      <c r="C25" s="59"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="2"/>
@@ -1912,6 +1912,7 @@
       <c r="U25" s="2"/>
     </row>
     <row r="26" spans="1:22" ht="15" x14ac:dyDescent="0.2">
+      <c r="D26"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -1924,7 +1925,7 @@
       <c r="U26" s="2"/>
     </row>
     <row r="27" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="C27"/>
+      <c r="C27" s="59"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -1937,7 +1938,7 @@
       <c r="U27" s="2"/>
     </row>
     <row r="28" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="D28" s="2"/>
+      <c r="D28"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>

--- a/results_cnn_subnetwork_evaluation/summary.xlsx
+++ b/results_cnn_subnetwork_evaluation/summary.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A357747-75C8-45D8-95B4-7700946ACF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="partialdata_20260407" sheetId="6" r:id="rId1"/>

--- a/results_cnn_subnetwork_evaluation/summary.xlsx
+++ b/results_cnn_subnetwork_evaluation/summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_cnn_subnetwork_evaluation_\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_cnn_subnetwork_evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A357747-75C8-45D8-95B4-7700946ACF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFB12DF-A583-4AEC-AD58-C902FC721171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="partialdata_20260407" sheetId="6" r:id="rId1"/>
@@ -366,7 +366,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -536,45 +536,81 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -928,10 +964,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="66"/>
+      <c r="B2" s="60"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -965,10 +1001,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="65" t="s">
+      <c r="M2" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="66"/>
+      <c r="N2" s="60"/>
       <c r="O2" s="37">
         <v>3.4649270444699574</v>
       </c>
@@ -996,10 +1032,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="66"/>
+      <c r="B3" s="60"/>
       <c r="C3" s="37">
         <v>93.273358766079312</v>
       </c>
@@ -1033,10 +1069,10 @@
         <f t="shared" ref="L3:L4" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="65" t="s">
+      <c r="M3" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="66"/>
+      <c r="N3" s="60"/>
       <c r="O3" s="37">
         <v>3.4672469457762647</v>
       </c>
@@ -1064,10 +1100,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="66"/>
+      <c r="B4" s="60"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -1101,10 +1137,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="65" t="s">
+      <c r="M4" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="66"/>
+      <c r="N4" s="60"/>
       <c r="O4" s="55">
         <v>2.4529187882918819</v>
       </c>
@@ -1132,31 +1168,31 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="66"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="60"/>
       <c r="J5" s="41"/>
       <c r="K5" s="41"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="65" t="s">
+      <c r="M5" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="66"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="61"/>
+      <c r="U5" s="60"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1304,603 +1340,603 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="65" t="s">
+      <c r="A8" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="67"/>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="66"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="63"/>
       <c r="J8" s="41"/>
       <c r="K8" s="41"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="65" t="s">
+      <c r="M8" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="67"/>
-      <c r="O8" s="67"/>
-      <c r="P8" s="67"/>
-      <c r="Q8" s="67"/>
-      <c r="R8" s="67"/>
-      <c r="S8" s="67"/>
-      <c r="T8" s="67"/>
-      <c r="U8" s="66"/>
+      <c r="N8" s="61"/>
+      <c r="O8" s="64"/>
+      <c r="P8" s="64"/>
+      <c r="Q8" s="64"/>
+      <c r="R8" s="64"/>
+      <c r="S8" s="64"/>
+      <c r="T8" s="64"/>
+      <c r="U8" s="63"/>
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="65" t="s">
+      <c r="A9" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="66"/>
-      <c r="C9" s="55">
-        <v>93.32548436116808</v>
-      </c>
-      <c r="D9" s="32">
-        <v>92.739539269370866</v>
-      </c>
-      <c r="E9" s="32">
-        <v>91.500872268214565</v>
-      </c>
-      <c r="F9" s="32">
-        <v>85.143369175627228</v>
-      </c>
-      <c r="G9" s="32">
-        <v>75.147299428772442</v>
-      </c>
-      <c r="H9" s="32">
-        <v>59.129842530356363</v>
-      </c>
-      <c r="I9" s="33">
-        <v>48.364190001643621</v>
+      <c r="B9" s="60"/>
+      <c r="C9" s="37">
+        <v>93.782740335124032</v>
+      </c>
+      <c r="D9" s="38">
+        <v>91.948208894540599</v>
+      </c>
+      <c r="E9" s="38">
+        <v>90.212980504444957</v>
+      </c>
+      <c r="F9" s="38">
+        <v>84.630388959535409</v>
+      </c>
+      <c r="G9" s="38">
+        <v>75.371093175546491</v>
+      </c>
+      <c r="H9" s="38">
+        <v>59.627211308056303</v>
+      </c>
+      <c r="I9" s="39">
+        <v>47.844185503334799</v>
       </c>
       <c r="J9" s="41" cm="1">
         <f t="array" ref="J9">-SUMPRODUCT((D1:H1-C1:G1)*(C9:G9+D9:H9)/2)</f>
-        <v>78.680994068576155</v>
+        <v>78.220843605913544</v>
       </c>
       <c r="K9" s="41" cm="1">
         <f t="array" ref="K9">-SUMPRODUCT((D1:I1-C1:H1)*(C9:H9+D9:I9)/2)</f>
-        <v>81.368344881876155</v>
+        <v>80.907628526198323</v>
       </c>
       <c r="L9" s="12" t="str">
         <f t="shared" ref="L9:L12" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:I9)&amp;","</f>
-        <v xml:space="preserve">    93.3254843611681, 92.7395392693709, 91.5008722682146, 85.1433691756272, 75.1472994287724, 59.1298425303564, 48.3641900016436,</v>
-      </c>
-      <c r="M9" s="65" t="s">
+        <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
+      </c>
+      <c r="M9" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="N9" s="66"/>
-      <c r="O9" s="55">
-        <v>3.667959563183556</v>
-      </c>
-      <c r="P9" s="32">
-        <v>3.989772059278164</v>
-      </c>
-      <c r="Q9" s="32">
-        <v>4.3227288020875694</v>
-      </c>
-      <c r="R9" s="32">
-        <v>4.691214264977404</v>
-      </c>
-      <c r="S9" s="32">
-        <v>9.351372365820513</v>
-      </c>
-      <c r="T9" s="32">
-        <v>11.12402361905577</v>
-      </c>
-      <c r="U9" s="33">
-        <v>9.7177921031411447</v>
+      <c r="N9" s="60"/>
+      <c r="O9" s="37">
+        <v>3.5391983918820551</v>
+      </c>
+      <c r="P9" s="38">
+        <v>4.1060038651541966</v>
+      </c>
+      <c r="Q9" s="38">
+        <v>4.774795806468676</v>
+      </c>
+      <c r="R9" s="38">
+        <v>5.3483339064680431</v>
+      </c>
+      <c r="S9" s="38">
+        <v>8.0994903921197494</v>
+      </c>
+      <c r="T9" s="38">
+        <v>10.59987402205407</v>
+      </c>
+      <c r="U9" s="39">
+        <v>8.7604668874903737</v>
       </c>
       <c r="V9" s="12" t="str">
         <f t="shared" ref="V9:V12" si="5">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O9:U9)&amp;","</f>
-        <v xml:space="preserve">    3.66795956318356, 3.98977205927816, 4.32272880208757, 4.6912142649774, 9.35137236582051, 11.1240236190558, 9.71779210314114,</v>
+        <v xml:space="preserve">    3.53919839188206, 4.1060038651542, 4.77479580646868, 5.34833390646804, 8.09949039211975, 10.5998740220541, 8.76046688749037,</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="70" t="s">
+      <c r="A10" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="69"/>
-      <c r="C10" s="55">
-        <v>93.029579263949799</v>
-      </c>
-      <c r="D10" s="32">
-        <v>91.699489903315182</v>
-      </c>
-      <c r="E10" s="32">
-        <v>90.230102913231647</v>
-      </c>
-      <c r="F10" s="32">
-        <v>85.684437869993104</v>
-      </c>
-      <c r="G10" s="32">
-        <v>76.604408342632709</v>
-      </c>
-      <c r="H10" s="32">
-        <v>60.525240991127369</v>
-      </c>
-      <c r="I10" s="33">
-        <v>50.546463781405251</v>
+      <c r="B10" s="63"/>
+      <c r="C10" s="40">
+        <v>93.226230330712227</v>
+      </c>
+      <c r="D10" s="93">
+        <v>91.83329152212967</v>
+      </c>
+      <c r="E10" s="93">
+        <v>90.325291164571794</v>
+      </c>
+      <c r="F10" s="93">
+        <v>85.383492360083878</v>
+      </c>
+      <c r="G10" s="93">
+        <v>76.567000291236639</v>
+      </c>
+      <c r="H10" s="93">
+        <v>59.41454222499042</v>
+      </c>
+      <c r="I10" s="42">
+        <v>50.563407411252108</v>
       </c>
       <c r="J10" s="41" cm="1">
         <f t="array" ref="J10">-SUMPRODUCT((D1:H1-C1:G1)*(C10:G10+D10:H10)/2)</f>
-        <v>78.394711603618248</v>
+        <v>78.369743178285859</v>
       </c>
       <c r="K10" s="41" cm="1">
         <f t="array" ref="K10">-SUMPRODUCT((D1:I1-C1:H1)*(C10:H10+D10:I10)/2)</f>
-        <v>81.17150422293156</v>
+        <v>81.11919191919192</v>
       </c>
       <c r="L10" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    93.0295792639498, 91.6994899033152, 90.2301029132316, 85.6844378699931, 76.6044083426327, 60.5252409911274, 50.5464637814053,</v>
-      </c>
-      <c r="M10" s="65" t="s">
+        <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
+      </c>
+      <c r="M10" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="N10" s="66"/>
-      <c r="O10" s="55">
-        <v>3.744976414623296</v>
-      </c>
-      <c r="P10" s="32">
-        <v>4.343666270045687</v>
-      </c>
-      <c r="Q10" s="32">
-        <v>4.7437159565801874</v>
-      </c>
-      <c r="R10" s="32">
-        <v>5.5306123777224894</v>
-      </c>
-      <c r="S10" s="32">
-        <v>8.3512102986812558</v>
-      </c>
-      <c r="T10" s="32">
-        <v>10.38527872584435</v>
-      </c>
-      <c r="U10" s="33">
-        <v>9.5213328677383782</v>
+      <c r="N10" s="60"/>
+      <c r="O10" s="40">
+        <v>3.945711842949601</v>
+      </c>
+      <c r="P10" s="93">
+        <v>4.8525950161134093</v>
+      </c>
+      <c r="Q10" s="93">
+        <v>4.4346894499148144</v>
+      </c>
+      <c r="R10" s="93">
+        <v>5.4810029574676529</v>
+      </c>
+      <c r="S10" s="93">
+        <v>8.4636725644600066</v>
+      </c>
+      <c r="T10" s="93">
+        <v>10.788297692871961</v>
+      </c>
+      <c r="U10" s="42">
+        <v>8.7433484877826491</v>
       </c>
       <c r="V10" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    3.7449764146233, 4.34366627004569, 4.74371595658019, 5.53061237772249, 8.35121029868126, 10.3852787258443, 9.52133286773838,</v>
+        <v xml:space="preserve">    3.9457118429496, 4.85259501611341, 4.43468944991481, 5.48100295746765, 8.46367256446001, 10.788297692872, 8.74334848778265,</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="65" t="s">
+      <c r="A11" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="66"/>
-      <c r="C11" s="55">
-        <v>92.961657684466715</v>
-      </c>
-      <c r="D11" s="32">
-        <v>91.581357393518388</v>
-      </c>
-      <c r="E11" s="32">
-        <v>90.473438351542839</v>
-      </c>
-      <c r="F11" s="32">
-        <v>86.603606720934735</v>
-      </c>
-      <c r="G11" s="32">
-        <v>77.903932271617123</v>
-      </c>
-      <c r="H11" s="32">
-        <v>59.567908603592286</v>
-      </c>
-      <c r="I11" s="33">
-        <v>48.445153793141223</v>
+      <c r="B11" s="60"/>
+      <c r="C11" s="40">
+        <v>93.004922187908207</v>
+      </c>
+      <c r="D11" s="93">
+        <v>91.518502178507859</v>
+      </c>
+      <c r="E11" s="93">
+        <v>89.729420958082102</v>
+      </c>
+      <c r="F11" s="93">
+        <v>83.348607398564567</v>
+      </c>
+      <c r="G11" s="93">
+        <v>74.087719905304837</v>
+      </c>
+      <c r="H11" s="93">
+        <v>57.917332041511322</v>
+      </c>
+      <c r="I11" s="42">
+        <v>48.007794185070807</v>
       </c>
       <c r="J11" s="41" cm="1">
         <f t="array" ref="J11">-SUMPRODUCT((D1:H1-C1:G1)*(C11:G11+D11:H11)/2)</f>
-        <v>78.631399853516598</v>
+        <v>77.501290236074709</v>
       </c>
       <c r="K11" s="41" cm="1">
         <f t="array" ref="K11">-SUMPRODUCT((D1:I1-C1:H1)*(C11:H11+D11:I11)/2)</f>
-        <v>81.331726413434936</v>
+        <v>80.14941839173926</v>
       </c>
       <c r="L11" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    92.9616576844667, 91.5813573935184, 90.4734383515428, 86.6036067209347, 77.9039322716171, 59.5679086035923, 48.4451537931412,</v>
-      </c>
-      <c r="M11" s="65" t="s">
+        <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
+      </c>
+      <c r="M11" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="N11" s="66"/>
-      <c r="O11" s="43">
-        <v>3.561541743303076</v>
-      </c>
-      <c r="P11" s="44">
-        <v>4.0732299909545224</v>
-      </c>
-      <c r="Q11" s="44">
-        <v>4.7078541322877587</v>
-      </c>
-      <c r="R11" s="44">
-        <v>5.7340237026421512</v>
-      </c>
-      <c r="S11" s="44">
-        <v>7.7315701222211866</v>
-      </c>
-      <c r="T11" s="44">
-        <v>8.7921119837631458</v>
-      </c>
-      <c r="U11" s="45">
-        <v>6.9480359155607783</v>
+      <c r="N11" s="60"/>
+      <c r="O11" s="40">
+        <v>3.690401528555848</v>
+      </c>
+      <c r="P11" s="93">
+        <v>4.2469367469027457</v>
+      </c>
+      <c r="Q11" s="93">
+        <v>4.4611096369834957</v>
+      </c>
+      <c r="R11" s="93">
+        <v>5.4089286426803449</v>
+      </c>
+      <c r="S11" s="93">
+        <v>9.092124974067179</v>
+      </c>
+      <c r="T11" s="93">
+        <v>10.83557708581068</v>
+      </c>
+      <c r="U11" s="42">
+        <v>9.2904800440053528</v>
       </c>
       <c r="V11" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    3.56154174330308, 4.07322999095452, 4.70785413228776, 5.73402370264215, 7.73157012222119, 8.79211198376315, 6.94803591556078,</v>
+        <v xml:space="preserve">    3.69040152855585, 4.24693674690275, 4.4611096369835, 5.40892864268034, 9.09212497406718, 10.8355770858107, 9.29048004400535,</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="65" t="s">
+      <c r="A12" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="55">
-        <v>93.033472031188253</v>
-      </c>
-      <c r="D12" s="32">
-        <v>91.100681378443298</v>
-      </c>
-      <c r="E12" s="32">
-        <v>89.756246449652096</v>
-      </c>
-      <c r="F12" s="32">
-        <v>83.92601147068747</v>
-      </c>
-      <c r="G12" s="32">
-        <v>76.162322626781645</v>
-      </c>
-      <c r="H12" s="32">
-        <v>59.765018151829473</v>
-      </c>
-      <c r="I12" s="33">
-        <v>48.291320282470707</v>
+      <c r="B12" s="60"/>
+      <c r="C12" s="43">
+        <v>93.123279613145442</v>
+      </c>
+      <c r="D12" s="44">
+        <v>91.674385879923975</v>
+      </c>
+      <c r="E12" s="44">
+        <v>89.698688281617194</v>
+      </c>
+      <c r="F12" s="44">
+        <v>84.957067102656595</v>
+      </c>
+      <c r="G12" s="44">
+        <v>75.939082518014857</v>
+      </c>
+      <c r="H12" s="44">
+        <v>59.995092229748238</v>
+      </c>
+      <c r="I12" s="45">
+        <v>48.440303693515233</v>
       </c>
       <c r="J12" s="41" cm="1">
         <f t="array" ref="J12">-SUMPRODUCT((D1:H1-C1:G1)*(C12:G12+D12:H12)/2)</f>
-        <v>77.792894690553823</v>
+        <v>78.078434213675436</v>
       </c>
       <c r="K12" s="41" cm="1">
         <f t="array" ref="K12">-SUMPRODUCT((D1:I1-C1:H1)*(C12:H12+D12:I12)/2)</f>
-        <v>80.49430315141133</v>
+        <v>80.789319111757024</v>
       </c>
       <c r="L12" s="12" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    93.0334720311883, 91.1006813784433, 89.7562464496521, 83.9260114706875, 76.1623226267816, 59.7650181518295, 48.2913202824707,</v>
-      </c>
-      <c r="M12" s="65" t="s">
+        <v xml:space="preserve">    93.1232796131454, 91.674385879924, 89.6986882816172, 84.9570671026566, 75.9390825180149, 59.9950922297482, 48.4403036935152,</v>
+      </c>
+      <c r="M12" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="N12" s="66"/>
-      <c r="O12" s="55">
-        <v>3.8568466007702029</v>
-      </c>
-      <c r="P12" s="32">
-        <v>4.6595572983107783</v>
-      </c>
-      <c r="Q12" s="32">
-        <v>4.7370792660764716</v>
-      </c>
-      <c r="R12" s="32">
-        <v>5.5210922070370687</v>
-      </c>
-      <c r="S12" s="32">
-        <v>8.0424472924959218</v>
-      </c>
-      <c r="T12" s="32">
-        <v>10.57495823817662</v>
-      </c>
-      <c r="U12" s="33">
-        <v>9.4501253063826809</v>
+      <c r="N12" s="60"/>
+      <c r="O12" s="43">
+        <v>3.8088682011350912</v>
+      </c>
+      <c r="P12" s="44">
+        <v>4.4783864386850611</v>
+      </c>
+      <c r="Q12" s="44">
+        <v>5.0849840192173117</v>
+      </c>
+      <c r="R12" s="44">
+        <v>5.0366327026230584</v>
+      </c>
+      <c r="S12" s="44">
+        <v>7.6643798786674449</v>
+      </c>
+      <c r="T12" s="44">
+        <v>10.05146904627655</v>
+      </c>
+      <c r="U12" s="45">
+        <v>9.821397671709315</v>
       </c>
       <c r="V12" s="12" t="str">
         <f t="shared" si="5"/>
-        <v xml:space="preserve">    3.8568466007702, 4.65955729831078, 4.73707926607647, 5.52109220703707, 8.04244729249592, 10.5749582381766, 9.45012530638268,</v>
+        <v xml:space="preserve">    3.80886820113509, 4.47838643868506, 5.08498401921731, 5.03663270262306, 7.66437987866744, 10.0514690462765, 9.82139767170931,</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="67"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="69"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="74"/>
       <c r="J13" s="41"/>
       <c r="K13" s="41"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="65" t="s">
+      <c r="M13" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="N13" s="67"/>
-      <c r="O13" s="68"/>
-      <c r="P13" s="68"/>
-      <c r="Q13" s="68"/>
-      <c r="R13" s="68"/>
-      <c r="S13" s="68"/>
-      <c r="T13" s="68"/>
-      <c r="U13" s="69"/>
+      <c r="N13" s="61"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="73"/>
+      <c r="Q13" s="73"/>
+      <c r="R13" s="73"/>
+      <c r="S13" s="73"/>
+      <c r="T13" s="73"/>
+      <c r="U13" s="74"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="65" t="s">
+      <c r="A14" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="55">
-        <v>91.808259587020672</v>
-      </c>
-      <c r="D14" s="32">
-        <v>90.918387413962634</v>
-      </c>
-      <c r="E14" s="32">
-        <v>89.996141835136996</v>
-      </c>
-      <c r="F14" s="32">
-        <v>87.690311623226279</v>
-      </c>
-      <c r="G14" s="32">
-        <v>84.300178490586703</v>
-      </c>
-      <c r="H14" s="32">
-        <v>60.212671966597178</v>
-      </c>
-      <c r="I14" s="33">
-        <v>42.728460742163293</v>
+      <c r="B14" s="60"/>
+      <c r="C14" s="37">
+        <v>92.969518190757128</v>
+      </c>
+      <c r="D14" s="38">
+        <v>91.851524090462149</v>
+      </c>
+      <c r="E14" s="38">
+        <v>90.756145526057011</v>
+      </c>
+      <c r="F14" s="38">
+        <v>87.253136561158271</v>
+      </c>
+      <c r="G14" s="38">
+        <v>81.178972136437139</v>
+      </c>
+      <c r="H14" s="38">
+        <v>57.386929529378847</v>
+      </c>
+      <c r="I14" s="39">
+        <v>44.855442809482213</v>
       </c>
       <c r="J14" s="41" cm="1">
         <f t="array" ref="J14">-SUMPRODUCT((D1:H1-C1:G1)*(C14:G14+D14:H14)/2)</f>
-        <v>79.048959405646542</v>
+        <v>79.079417714109411</v>
       </c>
       <c r="K14" s="41" cm="1">
         <f t="array" ref="K14">-SUMPRODUCT((D1:I1-C1:H1)*(C14:H14+D14:I14)/2)</f>
-        <v>81.622487723365552</v>
+        <v>81.635477022580943</v>
       </c>
       <c r="L14" s="12" t="str">
         <f t="shared" ref="L14:L17" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:I14)&amp;","</f>
-        <v xml:space="preserve">    91.8082595870207, 90.9183874139626, 89.996141835137, 87.6903116232263, 84.3001784905867, 60.2126719665972, 42.7284607421633,</v>
-      </c>
-      <c r="M14" s="65" t="s">
+        <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
+      </c>
+      <c r="M14" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="N14" s="66"/>
-      <c r="O14" s="55">
-        <v>3.5081436422345762</v>
-      </c>
-      <c r="P14" s="32">
-        <v>3.2318299507081201</v>
-      </c>
-      <c r="Q14" s="32">
-        <v>2.9043906528931069</v>
-      </c>
-      <c r="R14" s="32">
-        <v>3.2703414364377852</v>
-      </c>
-      <c r="S14" s="32">
-        <v>3.862191195058998</v>
-      </c>
-      <c r="T14" s="32">
-        <v>7.0362299825413483</v>
-      </c>
-      <c r="U14" s="33">
-        <v>3.4420784039601222</v>
+      <c r="N14" s="60"/>
+      <c r="O14" s="37">
+        <v>3.3991921823554931</v>
+      </c>
+      <c r="P14" s="38">
+        <v>3.6561489783789969</v>
+      </c>
+      <c r="Q14" s="38">
+        <v>3.4316179388806831</v>
+      </c>
+      <c r="R14" s="38">
+        <v>3.3610781227617821</v>
+      </c>
+      <c r="S14" s="38">
+        <v>5.2773835873092807</v>
+      </c>
+      <c r="T14" s="38">
+        <v>8.2027130196510409</v>
+      </c>
+      <c r="U14" s="39">
+        <v>5.203571843512913</v>
       </c>
       <c r="V14" s="12" t="str">
         <f t="shared" ref="V14:V17" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O14:U14)&amp;","</f>
-        <v xml:space="preserve">    3.50814364223458, 3.23182995070812, 2.90439065289311, 3.27034143643779, 3.862191195059, 7.03622998254135, 3.44207840396012,</v>
+        <v xml:space="preserve">    3.39919218235549, 3.656148978379, 3.43161793888068, 3.36107812276178, 5.27738358730928, 8.20271301965104, 5.20357184351291,</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="70" t="s">
+      <c r="A15" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="69"/>
-      <c r="C15" s="55">
-        <v>91.806402592871336</v>
-      </c>
-      <c r="D15" s="32">
-        <v>91.000000000000014</v>
-      </c>
-      <c r="E15" s="32">
-        <v>89.899705014749259</v>
-      </c>
-      <c r="F15" s="32">
-        <v>87.81909301406877</v>
-      </c>
-      <c r="G15" s="32">
-        <v>85.468643039011297</v>
-      </c>
-      <c r="H15" s="32">
-        <v>70.467985593877685</v>
-      </c>
-      <c r="I15" s="33">
-        <v>45.777178003269917</v>
+      <c r="B15" s="63"/>
+      <c r="C15" s="40">
+        <v>91.898721730580135</v>
+      </c>
+      <c r="D15" s="93">
+        <v>90.765995668936</v>
+      </c>
+      <c r="E15" s="93">
+        <v>89.705268500015848</v>
+      </c>
+      <c r="F15" s="93">
+        <v>87.959685349065893</v>
+      </c>
+      <c r="G15" s="93">
+        <v>85.750000720882824</v>
+      </c>
+      <c r="H15" s="93">
+        <v>71.387388010853613</v>
+      </c>
+      <c r="I15" s="42">
+        <v>45.596343105620853</v>
       </c>
       <c r="J15" s="41" cm="1">
         <f t="array" ref="J15">-SUMPRODUCT((D1:H1-C1:G1)*(C15:G15+D15:H15)/2)</f>
-        <v>79.696361488132837</v>
+        <v>79.700846821050931</v>
       </c>
       <c r="K15" s="41" cm="1">
         <f t="array" ref="K15">-SUMPRODUCT((D1:I1-C1:H1)*(C15:H15+D15:I15)/2)</f>
-        <v>82.60249057806152</v>
+        <v>82.625440098962798</v>
       </c>
       <c r="L15" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    91.8064025928713, 91, 89.8997050147493, 87.8190930140688, 85.4686430390113, 70.4679855938777, 45.7771780032699,</v>
-      </c>
-      <c r="M15" s="65" t="s">
+        <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
+      </c>
+      <c r="M15" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="66"/>
-      <c r="O15" s="55">
-        <v>3.30162613426437</v>
-      </c>
-      <c r="P15" s="32">
-        <v>2.7895411419086922</v>
-      </c>
-      <c r="Q15" s="32">
-        <v>2.4165108199523742</v>
-      </c>
-      <c r="R15" s="32">
-        <v>2.7123736733211721</v>
-      </c>
-      <c r="S15" s="32">
-        <v>3.8014726287512541</v>
-      </c>
-      <c r="T15" s="32">
-        <v>5.2299009938051402</v>
-      </c>
-      <c r="U15" s="33">
-        <v>2.1746822737589162</v>
+      <c r="N15" s="60"/>
+      <c r="O15" s="40">
+        <v>3.190312271555559</v>
+      </c>
+      <c r="P15" s="93">
+        <v>2.8828036064622768</v>
+      </c>
+      <c r="Q15" s="93">
+        <v>2.5884740771146331</v>
+      </c>
+      <c r="R15" s="93">
+        <v>2.6213450470877251</v>
+      </c>
+      <c r="S15" s="93">
+        <v>3.203569989687661</v>
+      </c>
+      <c r="T15" s="93">
+        <v>4.756712112750666</v>
+      </c>
+      <c r="U15" s="42">
+        <v>2.488810891584841</v>
       </c>
       <c r="V15" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    3.30162613426437, 2.78954114190869, 2.41651081995237, 2.71237367332117, 3.80147262875125, 5.22990099380514, 2.17468227375892,</v>
+        <v xml:space="preserve">    3.19031227155556, 2.88280360646228, 2.58847407711463, 2.62134504708773, 3.20356998968766, 4.75671211275067, 2.48881089158484,</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="55">
-        <v>93.12979927738705</v>
-      </c>
-      <c r="D16" s="32">
-        <v>92.072884136829316</v>
-      </c>
-      <c r="E16" s="32">
-        <v>90.991179277790764</v>
-      </c>
-      <c r="F16" s="32">
-        <v>86.488871010994899</v>
-      </c>
-      <c r="G16" s="32">
-        <v>78.849479666779118</v>
-      </c>
-      <c r="H16" s="32">
-        <v>59.403051352808703</v>
-      </c>
-      <c r="I16" s="33">
-        <v>48.981470427944863</v>
+      <c r="B16" s="60"/>
+      <c r="C16" s="40">
+        <v>93.044276622923505</v>
+      </c>
+      <c r="D16" s="93">
+        <v>91.935155148400938</v>
+      </c>
+      <c r="E16" s="93">
+        <v>90.94889229145582</v>
+      </c>
+      <c r="F16" s="93">
+        <v>85.952505356159378</v>
+      </c>
+      <c r="G16" s="93">
+        <v>78.915183810701947</v>
+      </c>
+      <c r="H16" s="93">
+        <v>59.442100133507502</v>
+      </c>
+      <c r="I16" s="42">
+        <v>49.533828147302302</v>
       </c>
       <c r="J16" s="41" cm="1">
         <f t="array" ref="J16">-SUMPRODUCT((D1:H1-C1:G1)*(C16:G16+D16:H16)/2)</f>
-        <v>78.960892467351215</v>
+        <v>78.834323321712716</v>
       </c>
       <c r="K16" s="41" cm="1">
         <f t="array" ref="K16">-SUMPRODUCT((D1:I1-C1:H1)*(C16:H16+D16:I16)/2)</f>
-        <v>81.670505511870061</v>
+        <v>81.55872152873296</v>
       </c>
       <c r="L16" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    93.1297992773871, 92.0728841368293, 90.9911792777908, 86.4888710109949, 78.8494796667791, 59.4030513528087, 48.9814704279449,</v>
-      </c>
-      <c r="M16" s="65" t="s">
+        <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
+      </c>
+      <c r="M16" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="N16" s="66"/>
-      <c r="O16" s="55">
-        <v>3.720535922449947</v>
-      </c>
-      <c r="P16" s="32">
-        <v>4.0622972018703303</v>
-      </c>
-      <c r="Q16" s="32">
-        <v>3.8973921609932098</v>
-      </c>
-      <c r="R16" s="32">
-        <v>4.4056182294833066</v>
-      </c>
-      <c r="S16" s="32">
-        <v>6.8043189964443149</v>
-      </c>
-      <c r="T16" s="32">
-        <v>10.63228683456753</v>
-      </c>
-      <c r="U16" s="33">
-        <v>8.6293638993197188</v>
+      <c r="N16" s="60"/>
+      <c r="O16" s="40">
+        <v>3.72078192123604</v>
+      </c>
+      <c r="P16" s="93">
+        <v>4.0467152776216686</v>
+      </c>
+      <c r="Q16" s="93">
+        <v>4.0235763627769954</v>
+      </c>
+      <c r="R16" s="93">
+        <v>4.4767633212331157</v>
+      </c>
+      <c r="S16" s="93">
+        <v>7.2019016527503927</v>
+      </c>
+      <c r="T16" s="93">
+        <v>10.04668436860082</v>
+      </c>
+      <c r="U16" s="42">
+        <v>9.2355901481835172</v>
       </c>
       <c r="V16" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    3.72053592244995, 4.06229720187033, 3.89739216099321, 4.40561822948331, 6.80431899644431, 10.6322868345675, 8.62936389931972,</v>
+        <v xml:space="preserve">    3.72078192123604, 4.04671527762167, 4.023576362777, 4.47676332123312, 7.20190165275039, 10.0466843686008, 9.23559014818352,</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="55">
-        <v>93.29405963719411</v>
-      </c>
-      <c r="D17" s="32">
-        <v>91.739729582435828</v>
-      </c>
-      <c r="E17" s="32">
-        <v>90.005885287358296</v>
-      </c>
-      <c r="F17" s="32">
-        <v>84.180898335337389</v>
-      </c>
-      <c r="G17" s="32">
-        <v>76.342811500676177</v>
-      </c>
-      <c r="H17" s="32">
-        <v>59.562899909745468</v>
-      </c>
-      <c r="I17" s="33">
-        <v>48.344573338293003</v>
+      <c r="B17" s="60"/>
+      <c r="C17" s="43">
+        <v>93.174110502686005</v>
+      </c>
+      <c r="D17" s="44">
+        <v>91.391724841910417</v>
+      </c>
+      <c r="E17" s="44">
+        <v>89.591539142495463</v>
+      </c>
+      <c r="F17" s="44">
+        <v>84.690597092823751</v>
+      </c>
+      <c r="G17" s="44">
+        <v>76.401347185817656</v>
+      </c>
+      <c r="H17" s="44">
+        <v>59.963667505774268</v>
+      </c>
+      <c r="I17" s="45">
+        <v>47.725577210875521</v>
       </c>
       <c r="J17" s="41" cm="1">
         <f t="array" ref="J17">-SUMPRODUCT((D1:H1-C1:G1)*(C17:G17+D17:H17)/2)</f>
-        <v>78.087574935769339</v>
+        <v>77.994698988168864</v>
       </c>
       <c r="K17" s="41" cm="1">
         <f t="array" ref="K17">-SUMPRODUCT((D1:I1-C1:H1)*(C17:H17+D17:I17)/2)</f>
-        <v>80.785261766970308</v>
+        <v>80.686930106085114</v>
       </c>
       <c r="L17" s="12" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    93.2940596371941, 91.7397295824358, 90.0058852873583, 84.1808983353374, 76.3428115006762, 59.5628999097455, 48.344573338293,</v>
-      </c>
-      <c r="M17" s="65" t="s">
+        <v xml:space="preserve">    93.174110502686, 91.3917248419104, 89.5915391424955, 84.6905970928238, 76.4013471858177, 59.9636675057743, 47.7255772108755,</v>
+      </c>
+      <c r="M17" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="N17" s="66"/>
-      <c r="O17" s="55">
-        <v>3.5976530252225301</v>
-      </c>
-      <c r="P17" s="32">
-        <v>4.5356023728221411</v>
-      </c>
-      <c r="Q17" s="32">
-        <v>4.6296560466546204</v>
-      </c>
-      <c r="R17" s="32">
-        <v>5.2864726273441152</v>
-      </c>
-      <c r="S17" s="32">
-        <v>8.2846675717539657</v>
-      </c>
-      <c r="T17" s="32">
-        <v>10.25067270866937</v>
-      </c>
-      <c r="U17" s="33">
-        <v>9.5941688433330885</v>
+      <c r="N17" s="60"/>
+      <c r="O17" s="43">
+        <v>3.8766021792735019</v>
+      </c>
+      <c r="P17" s="44">
+        <v>4.8126411406228078</v>
+      </c>
+      <c r="Q17" s="44">
+        <v>4.6512210016047986</v>
+      </c>
+      <c r="R17" s="44">
+        <v>5.2416066355763284</v>
+      </c>
+      <c r="S17" s="44">
+        <v>8.0769588602235256</v>
+      </c>
+      <c r="T17" s="44">
+        <v>10.657363307561541</v>
+      </c>
+      <c r="U17" s="45">
+        <v>9.200486032966916</v>
       </c>
       <c r="V17" s="12" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    3.59765302522253, 4.53560237282214, 4.62965604665462, 5.28647262734412, 8.28466757175397, 10.2506727086694, 9.59416884333309,</v>
+        <v xml:space="preserve">    3.8766021792735, 4.81264114062281, 4.6512210016048, 5.24160663557633, 8.07695886022353, 10.6573633075615, 9.20048603296692,</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -1986,10 +2022,10 @@
       <c r="V19" s="1"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="60"/>
+      <c r="B20" s="66"/>
       <c r="C20" s="47">
         <v>92.567111769713335</v>
       </c>
@@ -2017,10 +2053,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:I20)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M20" s="59" t="s">
+      <c r="M20" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="N20" s="60"/>
+      <c r="N20" s="66"/>
       <c r="O20" s="46">
         <v>3.88093621561358</v>
       </c>
@@ -2048,10 +2084,10 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="59" t="s">
+      <c r="A21" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="60"/>
+      <c r="B21" s="66"/>
       <c r="C21" s="47">
         <v>92.866950218042462</v>
       </c>
@@ -2079,10 +2115,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M21" s="59" t="s">
+      <c r="M21" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="N21" s="60"/>
+      <c r="N21" s="66"/>
       <c r="O21" s="47">
         <v>3.8319643020864191</v>
       </c>
@@ -2110,10 +2146,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="60"/>
+      <c r="B22" s="66"/>
       <c r="C22" s="34">
         <v>87.268396410214976</v>
       </c>
@@ -2141,10 +2177,10 @@
         <f t="shared" ref="L22:L25" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:I22)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M22" s="59" t="s">
+      <c r="M22" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="N22" s="60"/>
+      <c r="N22" s="66"/>
       <c r="O22" s="34">
         <v>2.610595868561878</v>
       </c>
@@ -2172,31 +2208,31 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="59" t="s">
+      <c r="A23" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="B23" s="63"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63"/>
-      <c r="F23" s="63"/>
-      <c r="G23" s="63"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="60"/>
+      <c r="B23" s="67"/>
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="67"/>
+      <c r="G23" s="67"/>
+      <c r="H23" s="67"/>
+      <c r="I23" s="66"/>
       <c r="J23" s="50"/>
       <c r="K23" s="50"/>
       <c r="L23" s="1"/>
-      <c r="M23" s="59" t="s">
+      <c r="M23" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="N23" s="63"/>
-      <c r="O23" s="63"/>
-      <c r="P23" s="63"/>
-      <c r="Q23" s="63"/>
-      <c r="R23" s="63"/>
-      <c r="S23" s="63"/>
-      <c r="T23" s="63"/>
-      <c r="U23" s="60"/>
+      <c r="N23" s="67"/>
+      <c r="O23" s="67"/>
+      <c r="P23" s="67"/>
+      <c r="Q23" s="67"/>
+      <c r="R23" s="67"/>
+      <c r="S23" s="67"/>
+      <c r="T23" s="67"/>
+      <c r="U23" s="66"/>
       <c r="V23" s="1"/>
     </row>
     <row r="24" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -2332,555 +2368,555 @@
       </c>
     </row>
     <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="59" t="s">
+      <c r="A26" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="B26" s="63"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
-      <c r="I26" s="60"/>
+      <c r="B26" s="67"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="68"/>
+      <c r="G26" s="68"/>
+      <c r="H26" s="68"/>
+      <c r="I26" s="69"/>
       <c r="J26" s="50"/>
       <c r="K26" s="50"/>
       <c r="L26" s="1"/>
-      <c r="M26" s="59" t="s">
+      <c r="M26" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="N26" s="63"/>
-      <c r="O26" s="63"/>
-      <c r="P26" s="63"/>
-      <c r="Q26" s="63"/>
-      <c r="R26" s="63"/>
-      <c r="S26" s="63"/>
-      <c r="T26" s="63"/>
-      <c r="U26" s="60"/>
+      <c r="N26" s="67"/>
+      <c r="O26" s="68"/>
+      <c r="P26" s="68"/>
+      <c r="Q26" s="68"/>
+      <c r="R26" s="68"/>
+      <c r="S26" s="68"/>
+      <c r="T26" s="68"/>
+      <c r="U26" s="69"/>
       <c r="V26" s="1"/>
     </row>
     <row r="27" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="59" t="s">
+      <c r="A27" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="60"/>
-      <c r="C27" s="34">
-        <v>92.868050634154315</v>
-      </c>
-      <c r="D27" s="35">
-        <v>92.288231222045297</v>
-      </c>
-      <c r="E27" s="35">
-        <v>91.054287148035144</v>
-      </c>
-      <c r="F27" s="35">
-        <v>84.437885333085376</v>
-      </c>
-      <c r="G27" s="35">
-        <v>74.253673383599548</v>
-      </c>
-      <c r="H27" s="35">
-        <v>57.552195558991649</v>
-      </c>
-      <c r="I27" s="36">
-        <v>45.560977654736433</v>
+      <c r="B27" s="66"/>
+      <c r="C27" s="46">
+        <v>93.403798109785029</v>
+      </c>
+      <c r="D27" s="47">
+        <v>91.51700700493744</v>
+      </c>
+      <c r="E27" s="47">
+        <v>89.749880462689262</v>
+      </c>
+      <c r="F27" s="47">
+        <v>83.99730958119234</v>
+      </c>
+      <c r="G27" s="47">
+        <v>74.394962965986878</v>
+      </c>
+      <c r="H27" s="47">
+        <v>58.095582470498513</v>
+      </c>
+      <c r="I27" s="48">
+        <v>44.434812706207254</v>
       </c>
       <c r="J27" s="50"/>
       <c r="K27" s="50"/>
       <c r="L27" s="1" t="str">
         <f t="shared" ref="L27:L30" si="10">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
-        <v xml:space="preserve">    92.8680506341543, 92.2882312220453, 91.0542871480351, 84.4378853330854, 74.2536733835995, 57.5521955589916, 45.5609776547364,</v>
-      </c>
-      <c r="M27" s="59" t="s">
+        <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
+      </c>
+      <c r="M27" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="N27" s="60"/>
-      <c r="O27" s="34">
-        <v>4.0949495507503526</v>
-      </c>
-      <c r="P27" s="35">
-        <v>4.4354851591423481</v>
-      </c>
-      <c r="Q27" s="35">
-        <v>4.6437372111598876</v>
-      </c>
-      <c r="R27" s="35">
-        <v>5.0311660763107948</v>
-      </c>
-      <c r="S27" s="35">
-        <v>9.8512038160577102</v>
-      </c>
-      <c r="T27" s="35">
-        <v>11.57485796488027</v>
-      </c>
-      <c r="U27" s="36">
-        <v>10.571075661324681</v>
+      <c r="N27" s="66"/>
+      <c r="O27" s="46">
+        <v>3.9553866501853321</v>
+      </c>
+      <c r="P27" s="47">
+        <v>4.517630835861226</v>
+      </c>
+      <c r="Q27" s="47">
+        <v>5.2125425794506972</v>
+      </c>
+      <c r="R27" s="47">
+        <v>5.6477461387684551</v>
+      </c>
+      <c r="S27" s="47">
+        <v>8.6090564713117175</v>
+      </c>
+      <c r="T27" s="47">
+        <v>11.357157347254571</v>
+      </c>
+      <c r="U27" s="48">
+        <v>9.3757621724255777</v>
       </c>
       <c r="V27" s="1" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    4.09494955075035, 4.43548515914235, 4.64373721115989, 5.03116607631079, 9.85120381605771, 11.5748579648803, 10.5710756613247,</v>
+        <v xml:space="preserve">    3.95538665018533, 4.51763083586123, 5.2125425794507, 5.64774613876846, 8.60905647131172, 11.3571573472546, 9.37576217242558,</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="59" t="s">
+      <c r="A28" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="60"/>
-      <c r="C28" s="34">
-        <v>92.513598322189821</v>
-      </c>
-      <c r="D28" s="35">
-        <v>91.261446870594469</v>
-      </c>
-      <c r="E28" s="35">
-        <v>89.758265941661861</v>
-      </c>
-      <c r="F28" s="35">
-        <v>85.044465656129674</v>
-      </c>
-      <c r="G28" s="35">
-        <v>75.898843968080286</v>
-      </c>
-      <c r="H28" s="35">
-        <v>59.465611837116732</v>
-      </c>
-      <c r="I28" s="36">
-        <v>48.473156490254198</v>
+      <c r="B28" s="66"/>
+      <c r="C28" s="49">
+        <v>92.778947400409621</v>
+      </c>
+      <c r="D28" s="94">
+        <v>91.450368996373655</v>
+      </c>
+      <c r="E28" s="94">
+        <v>89.879480954542075</v>
+      </c>
+      <c r="F28" s="94">
+        <v>84.748756470336986</v>
+      </c>
+      <c r="G28" s="94">
+        <v>75.627608782580538</v>
+      </c>
+      <c r="H28" s="94">
+        <v>58.300265665116903</v>
+      </c>
+      <c r="I28" s="51">
+        <v>48.584106437626268</v>
       </c>
       <c r="J28" s="50"/>
       <c r="K28" s="50"/>
       <c r="L28" s="1" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">    92.5135983221898, 91.2614468705945, 89.7582659416619, 85.0444656561297, 75.8988439680803, 59.4656118371167, 48.4731564902542,</v>
-      </c>
-      <c r="M28" s="59" t="s">
+        <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
+      </c>
+      <c r="M28" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="N28" s="60"/>
-      <c r="O28" s="34">
-        <v>4.2171731523020446</v>
-      </c>
-      <c r="P28" s="35">
-        <v>4.6702984752282681</v>
-      </c>
-      <c r="Q28" s="35">
-        <v>5.0608860361047316</v>
-      </c>
-      <c r="R28" s="35">
-        <v>5.9068575059271318</v>
-      </c>
-      <c r="S28" s="35">
-        <v>8.5966909141817851</v>
-      </c>
-      <c r="T28" s="35">
-        <v>10.771320326074211</v>
-      </c>
-      <c r="U28" s="36">
-        <v>10.23603152809228</v>
+      <c r="N28" s="66"/>
+      <c r="O28" s="49">
+        <v>4.3743918396131134</v>
+      </c>
+      <c r="P28" s="94">
+        <v>5.1779143655465321</v>
+      </c>
+      <c r="Q28" s="94">
+        <v>4.8362705721377752</v>
+      </c>
+      <c r="R28" s="94">
+        <v>5.6797782301447892</v>
+      </c>
+      <c r="S28" s="94">
+        <v>9.0190902977959446</v>
+      </c>
+      <c r="T28" s="94">
+        <v>11.000258135261941</v>
+      </c>
+      <c r="U28" s="51">
+        <v>9.2918474149187738</v>
       </c>
       <c r="V28" s="1" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    4.21717315230204, 4.67029847522827, 5.06088603610473, 5.90685750592713, 8.59669091418179, 10.7713203260742, 10.2360315280923,</v>
+        <v xml:space="preserve">    4.37439183961311, 5.17791436554653, 4.83627057213778, 5.67977823014479, 9.01909029779594, 11.0002581352619, 9.29184741491877,</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="59" t="s">
+      <c r="A29" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="B29" s="60"/>
-      <c r="C29" s="52">
-        <v>92.570176373736686</v>
-      </c>
-      <c r="D29" s="53">
-        <v>91.035116753825534</v>
-      </c>
-      <c r="E29" s="53">
-        <v>89.995984735900805</v>
-      </c>
-      <c r="F29" s="53">
-        <v>86.101239818995751</v>
-      </c>
-      <c r="G29" s="53">
-        <v>77.099560389949318</v>
-      </c>
-      <c r="H29" s="53">
-        <v>57.996429145301242</v>
-      </c>
-      <c r="I29" s="54">
-        <v>44.399943110932981</v>
+      <c r="B29" s="66"/>
+      <c r="C29" s="49">
+        <v>92.492055194421354</v>
+      </c>
+      <c r="D29" s="94">
+        <v>91.055738083245984</v>
+      </c>
+      <c r="E29" s="94">
+        <v>89.241264887762341</v>
+      </c>
+      <c r="F29" s="94">
+        <v>82.713601809643421</v>
+      </c>
+      <c r="G29" s="94">
+        <v>73.133677048774885</v>
+      </c>
+      <c r="H29" s="94">
+        <v>56.229205901331248</v>
+      </c>
+      <c r="I29" s="51">
+        <v>43.695396708102962</v>
       </c>
       <c r="J29" s="50"/>
       <c r="K29" s="50"/>
       <c r="L29" s="1" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">    92.5701763737367, 91.0351167538255, 89.9959847359008, 86.1012398189958, 77.0995603899493, 57.9964291453012, 44.399943110933,</v>
-      </c>
-      <c r="M29" s="59" t="s">
+        <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
+      </c>
+      <c r="M29" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="N29" s="60"/>
-      <c r="O29" s="52">
-        <v>3.882028195540002</v>
-      </c>
-      <c r="P29" s="53">
-        <v>4.4292663319519576</v>
-      </c>
-      <c r="Q29" s="53">
-        <v>5.1354581403320241</v>
-      </c>
-      <c r="R29" s="53">
-        <v>5.8685355921558013</v>
-      </c>
-      <c r="S29" s="53">
-        <v>8.0663639251543504</v>
-      </c>
-      <c r="T29" s="53">
-        <v>9.5110854192429173</v>
-      </c>
-      <c r="U29" s="54">
-        <v>8.058131505188614</v>
+      <c r="N29" s="66"/>
+      <c r="O29" s="49">
+        <v>4.0986250609792014</v>
+      </c>
+      <c r="P29" s="94">
+        <v>4.5926443490712341</v>
+      </c>
+      <c r="Q29" s="94">
+        <v>4.8521598807380544</v>
+      </c>
+      <c r="R29" s="94">
+        <v>5.8188919126166327</v>
+      </c>
+      <c r="S29" s="94">
+        <v>9.5088987825376563</v>
+      </c>
+      <c r="T29" s="94">
+        <v>11.32839542788332</v>
+      </c>
+      <c r="U29" s="51">
+        <v>10.62887090695313</v>
       </c>
       <c r="V29" s="1" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    3.88202819554, 4.42926633195196, 5.13545814033202, 5.8685355921558, 8.06636392515435, 9.51108541924292, 8.05813150518861,</v>
+        <v xml:space="preserve">    4.0986250609792, 4.59264434907123, 4.85215988073805, 5.81889191261663, 9.50889878253766, 11.3283954278833, 10.6288709069531,</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="59" t="s">
+      <c r="A30" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="60"/>
-      <c r="C30" s="34">
-        <v>92.515649858336417</v>
-      </c>
-      <c r="D30" s="35">
-        <v>90.633837177608882</v>
-      </c>
-      <c r="E30" s="35">
-        <v>89.218749027706451</v>
-      </c>
-      <c r="F30" s="35">
-        <v>83.159104859904048</v>
-      </c>
-      <c r="G30" s="35">
-        <v>75.205406346603183</v>
-      </c>
-      <c r="H30" s="35">
-        <v>58.328595951322271</v>
-      </c>
-      <c r="I30" s="36">
-        <v>44.663256049071087</v>
+      <c r="B30" s="66"/>
+      <c r="C30" s="52">
+        <v>92.657174075741665</v>
+      </c>
+      <c r="D30" s="53">
+        <v>91.208050814372243</v>
+      </c>
+      <c r="E30" s="53">
+        <v>89.170455678091372</v>
+      </c>
+      <c r="F30" s="53">
+        <v>84.474616062770011</v>
+      </c>
+      <c r="G30" s="53">
+        <v>75.066668593640316</v>
+      </c>
+      <c r="H30" s="53">
+        <v>58.520340993368222</v>
+      </c>
+      <c r="I30" s="54">
+        <v>44.786141592049418</v>
       </c>
       <c r="J30" s="58"/>
       <c r="K30" s="58"/>
       <c r="L30" s="1" t="str">
         <f t="shared" si="10"/>
-        <v xml:space="preserve">    92.5156498583364, 90.6338371776089, 89.2187490277065, 83.159104859904, 75.2054063466032, 58.3285959513223, 44.6632560490711,</v>
-      </c>
-      <c r="M30" s="59" t="s">
+        <v xml:space="preserve">    92.6571740757417, 91.2080508143722, 89.1704556780914, 84.47461606277, 75.0666685936403, 58.5203409933682, 44.7861415920494,</v>
+      </c>
+      <c r="M30" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="N30" s="60"/>
-      <c r="O30" s="34">
-        <v>4.2818937520906779</v>
-      </c>
-      <c r="P30" s="35">
-        <v>5.0215820890726173</v>
-      </c>
-      <c r="Q30" s="35">
-        <v>5.2048209810817641</v>
-      </c>
-      <c r="R30" s="35">
-        <v>6.0125954692045056</v>
-      </c>
-      <c r="S30" s="35">
-        <v>8.4472284006849367</v>
-      </c>
-      <c r="T30" s="35">
-        <v>11.323085110814951</v>
-      </c>
-      <c r="U30" s="36">
-        <v>10.33126321411414</v>
+      <c r="N30" s="66"/>
+      <c r="O30" s="52">
+        <v>4.2589004392769629</v>
+      </c>
+      <c r="P30" s="53">
+        <v>4.8517186601265534</v>
+      </c>
+      <c r="Q30" s="53">
+        <v>5.6717673083496472</v>
+      </c>
+      <c r="R30" s="53">
+        <v>5.3079507961921779</v>
+      </c>
+      <c r="S30" s="53">
+        <v>7.7884705615072454</v>
+      </c>
+      <c r="T30" s="53">
+        <v>10.595563377926201</v>
+      </c>
+      <c r="U30" s="54">
+        <v>10.945843294214329</v>
       </c>
       <c r="V30" s="1" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    4.28189375209068, 5.02158208907262, 5.20482098108176, 6.01259546920451, 8.44722840068494, 11.323085110815, 10.3312632141141,</v>
+        <v xml:space="preserve">    4.25890043927696, 4.85171866012655, 5.67176730834965, 5.30795079619218, 7.78847056150725, 10.5955633779262, 10.9458432942143,</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="59" t="s">
+      <c r="A31" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="63"/>
-      <c r="C31" s="64"/>
-      <c r="D31" s="64"/>
-      <c r="E31" s="64"/>
-      <c r="F31" s="64"/>
-      <c r="G31" s="64"/>
-      <c r="H31" s="64"/>
-      <c r="I31" s="62"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="71"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="72"/>
       <c r="J31" s="50"/>
       <c r="K31" s="50"/>
       <c r="L31" s="1"/>
-      <c r="M31" s="59" t="s">
+      <c r="M31" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="N31" s="63"/>
-      <c r="O31" s="64"/>
-      <c r="P31" s="64"/>
-      <c r="Q31" s="64"/>
-      <c r="R31" s="64"/>
-      <c r="S31" s="64"/>
-      <c r="T31" s="64"/>
-      <c r="U31" s="62"/>
+      <c r="N31" s="67"/>
+      <c r="O31" s="71"/>
+      <c r="P31" s="71"/>
+      <c r="Q31" s="71"/>
+      <c r="R31" s="71"/>
+      <c r="S31" s="71"/>
+      <c r="T31" s="71"/>
+      <c r="U31" s="72"/>
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="59" t="s">
+      <c r="A32" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="60"/>
-      <c r="C32" s="34">
-        <v>91.365503103283018</v>
-      </c>
-      <c r="D32" s="35">
-        <v>90.485891056064375</v>
-      </c>
-      <c r="E32" s="35">
-        <v>89.568582528718636</v>
-      </c>
-      <c r="F32" s="35">
-        <v>87.35503422782692</v>
-      </c>
-      <c r="G32" s="35">
-        <v>83.775802183320806</v>
-      </c>
-      <c r="H32" s="35">
-        <v>59.664242373274107</v>
-      </c>
-      <c r="I32" s="36">
-        <v>38.734493305012087</v>
+      <c r="B32" s="66"/>
+      <c r="C32" s="46">
+        <v>92.603769819293618</v>
+      </c>
+      <c r="D32" s="47">
+        <v>91.431947068352812</v>
+      </c>
+      <c r="E32" s="47">
+        <v>90.390795042999585</v>
+      </c>
+      <c r="F32" s="47">
+        <v>86.789562828222273</v>
+      </c>
+      <c r="G32" s="47">
+        <v>80.615554033052248</v>
+      </c>
+      <c r="H32" s="47">
+        <v>56.609578553133908</v>
+      </c>
+      <c r="I32" s="48">
+        <v>41.27928062292434</v>
       </c>
       <c r="J32" s="50"/>
       <c r="K32" s="50"/>
       <c r="L32" s="1" t="str">
         <f t="shared" ref="L32:L35" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
-        <v xml:space="preserve">    91.365503103283, 90.4858910560644, 89.5685825287186, 87.3550342278269, 83.7758021833208, 59.6642423732741, 38.7344933050121,</v>
-      </c>
-      <c r="M32" s="59" t="s">
+        <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
+      </c>
+      <c r="M32" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="N32" s="60"/>
-      <c r="O32" s="34">
-        <v>3.8096312747348571</v>
-      </c>
-      <c r="P32" s="35">
-        <v>3.3823322749479061</v>
-      </c>
-      <c r="Q32" s="35">
-        <v>3.1901414384399041</v>
-      </c>
-      <c r="R32" s="35">
-        <v>3.435608860758363</v>
-      </c>
-      <c r="S32" s="35">
-        <v>3.9801135842717961</v>
-      </c>
-      <c r="T32" s="35">
-        <v>7.4065519031840097</v>
-      </c>
-      <c r="U32" s="36">
-        <v>4.3412957141341879</v>
+      <c r="N32" s="66"/>
+      <c r="O32" s="46">
+        <v>3.708759274801273</v>
+      </c>
+      <c r="P32" s="47">
+        <v>3.9640390541215931</v>
+      </c>
+      <c r="Q32" s="47">
+        <v>3.7067998106756881</v>
+      </c>
+      <c r="R32" s="47">
+        <v>3.667452632531309</v>
+      </c>
+      <c r="S32" s="47">
+        <v>5.7548227051500218</v>
+      </c>
+      <c r="T32" s="47">
+        <v>8.5366536877555248</v>
+      </c>
+      <c r="U32" s="48">
+        <v>6.3187793027043018</v>
       </c>
       <c r="V32" s="1" t="str">
         <f t="shared" ref="V32:V35" si="12">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O32:U32)&amp;","</f>
-        <v xml:space="preserve">    3.80963127473486, 3.38233227494791, 3.1901414384399, 3.43560886075836, 3.9801135842718, 7.40655190318401, 4.34129571413419,</v>
+        <v xml:space="preserve">    3.70875927480127, 3.96403905412159, 3.70679981067569, 3.66745263253131, 5.75482270515002, 8.53665368775552, 6.3187793027043,</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="61" t="s">
+      <c r="A33" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="62"/>
-      <c r="C33" s="34">
-        <v>91.352017689458577</v>
-      </c>
-      <c r="D33" s="35">
-        <v>90.612646908845178</v>
-      </c>
-      <c r="E33" s="35">
-        <v>89.673109045448143</v>
-      </c>
-      <c r="F33" s="35">
-        <v>87.570648852891097</v>
-      </c>
-      <c r="G33" s="35">
-        <v>85.153610116106222</v>
-      </c>
-      <c r="H33" s="35">
-        <v>70.154101376724071</v>
-      </c>
-      <c r="I33" s="36">
-        <v>44.255354014211143</v>
+      <c r="B33" s="69"/>
+      <c r="C33" s="49">
+        <v>91.377634404932721</v>
+      </c>
+      <c r="D33" s="94">
+        <v>90.405373333245066</v>
+      </c>
+      <c r="E33" s="94">
+        <v>89.371480308332721</v>
+      </c>
+      <c r="F33" s="94">
+        <v>87.60989862639515</v>
+      </c>
+      <c r="G33" s="94">
+        <v>85.537230701510694</v>
+      </c>
+      <c r="H33" s="94">
+        <v>70.930708745421484</v>
+      </c>
+      <c r="I33" s="51">
+        <v>44.097326232806537</v>
       </c>
       <c r="J33" s="50"/>
       <c r="K33" s="50"/>
       <c r="L33" s="1" t="str">
         <f t="shared" si="11"/>
-        <v xml:space="preserve">    91.3520176894586, 90.6126469088452, 89.6731090454481, 87.5706488528911, 85.1536101161062, 70.1541013767241, 44.2553540142111,</v>
-      </c>
-      <c r="M33" s="59" t="s">
+        <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
+      </c>
+      <c r="M33" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="N33" s="60"/>
-      <c r="O33" s="34">
-        <v>3.6410788132464011</v>
-      </c>
-      <c r="P33" s="35">
-        <v>3.0474479281352909</v>
-      </c>
-      <c r="Q33" s="35">
-        <v>2.5295084567057469</v>
-      </c>
-      <c r="R33" s="35">
-        <v>2.7268738132327659</v>
-      </c>
-      <c r="S33" s="35">
-        <v>4.0335194528578784</v>
-      </c>
-      <c r="T33" s="35">
-        <v>5.245193605897664</v>
-      </c>
-      <c r="U33" s="36">
-        <v>2.5110804834384211</v>
+      <c r="N33" s="66"/>
+      <c r="O33" s="49">
+        <v>3.5684194304484111</v>
+      </c>
+      <c r="P33" s="94">
+        <v>3.0347581440341318</v>
+      </c>
+      <c r="Q33" s="94">
+        <v>2.754130276526872</v>
+      </c>
+      <c r="R33" s="94">
+        <v>2.7768782002466339</v>
+      </c>
+      <c r="S33" s="94">
+        <v>3.3184641894178428</v>
+      </c>
+      <c r="T33" s="94">
+        <v>4.9795199020249923</v>
+      </c>
+      <c r="U33" s="51">
+        <v>2.9223071611371929</v>
       </c>
       <c r="V33" s="1" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    3.6410788132464, 3.04744792813529, 2.52950845670575, 2.72687381323277, 4.03351945285788, 5.24519360589766, 2.51108048343842,</v>
+        <v xml:space="preserve">    3.56841943044841, 3.03475814403413, 2.75413027652687, 2.77687820024663, 3.31846418941784, 4.97951990202499, 2.92230716113719,</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="59" t="s">
+      <c r="A34" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="B34" s="60"/>
-      <c r="C34" s="34">
-        <v>92.61946302134767</v>
-      </c>
-      <c r="D34" s="35">
-        <v>91.641845498508658</v>
-      </c>
-      <c r="E34" s="35">
-        <v>90.604490520989373</v>
-      </c>
-      <c r="F34" s="35">
-        <v>86.028930620603035</v>
-      </c>
-      <c r="G34" s="35">
-        <v>77.869547765340229</v>
-      </c>
-      <c r="H34" s="35">
-        <v>58.066616072179237</v>
-      </c>
-      <c r="I34" s="36">
-        <v>44.282072681774139</v>
+      <c r="B34" s="66"/>
+      <c r="C34" s="49">
+        <v>92.603715202692385</v>
+      </c>
+      <c r="D34" s="94">
+        <v>91.484997502720319</v>
+      </c>
+      <c r="E34" s="94">
+        <v>90.630171299324857</v>
+      </c>
+      <c r="F34" s="94">
+        <v>85.342034697064548</v>
+      </c>
+      <c r="G34" s="94">
+        <v>78.208607944308184</v>
+      </c>
+      <c r="H34" s="94">
+        <v>58.188767254712552</v>
+      </c>
+      <c r="I34" s="51">
+        <v>45.468919562576168</v>
       </c>
       <c r="J34" s="50"/>
       <c r="K34" s="50"/>
       <c r="L34" s="1" t="str">
         <f t="shared" si="11"/>
-        <v xml:space="preserve">    92.6194630213477, 91.6418454985087, 90.6044905209894, 86.028930620603, 77.8695477653402, 58.0666160721792, 44.2820726817741,</v>
-      </c>
-      <c r="M34" s="59" t="s">
+        <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
+      </c>
+      <c r="M34" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="N34" s="60"/>
-      <c r="O34" s="34">
-        <v>4.1202488894386304</v>
-      </c>
-      <c r="P34" s="35">
-        <v>4.4587262447220368</v>
-      </c>
-      <c r="Q34" s="35">
-        <v>4.1451701238630649</v>
-      </c>
-      <c r="R34" s="35">
-        <v>4.7547668035033421</v>
-      </c>
-      <c r="S34" s="35">
-        <v>7.3962800398529813</v>
-      </c>
-      <c r="T34" s="35">
-        <v>11.13409225199972</v>
-      </c>
-      <c r="U34" s="36">
-        <v>10.21410985821676</v>
+      <c r="N34" s="66"/>
+      <c r="O34" s="49">
+        <v>4.0727132923350373</v>
+      </c>
+      <c r="P34" s="94">
+        <v>4.4231285957629458</v>
+      </c>
+      <c r="Q34" s="94">
+        <v>4.3011534303531356</v>
+      </c>
+      <c r="R34" s="94">
+        <v>4.8453894583465429</v>
+      </c>
+      <c r="S34" s="94">
+        <v>7.5589700135942426</v>
+      </c>
+      <c r="T34" s="94">
+        <v>10.3740336621021</v>
+      </c>
+      <c r="U34" s="51">
+        <v>10.707618741543239</v>
       </c>
       <c r="V34" s="1" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    4.12024888943863, 4.45872624472204, 4.14517012386306, 4.75476680350334, 7.39628003985298, 11.1340922519997, 10.2141098582168,</v>
+        <v xml:space="preserve">    4.07271329233504, 4.42312859576295, 4.30115343035314, 4.84538945834654, 7.55897001359424, 10.3740336621021, 10.7076187415432,</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="59" t="s">
+      <c r="A35" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="B35" s="60"/>
-      <c r="C35" s="34">
-        <v>92.836313492728166</v>
-      </c>
-      <c r="D35" s="35">
-        <v>91.35902579070337</v>
-      </c>
-      <c r="E35" s="35">
-        <v>89.600386013681359</v>
-      </c>
-      <c r="F35" s="35">
-        <v>83.549429512462467</v>
-      </c>
-      <c r="G35" s="35">
-        <v>75.443451304684089</v>
-      </c>
-      <c r="H35" s="35">
-        <v>58.040988875657007</v>
-      </c>
-      <c r="I35" s="36">
-        <v>44.45694317203499</v>
+      <c r="B35" s="66"/>
+      <c r="C35" s="52">
+        <v>92.692685851985146</v>
+      </c>
+      <c r="D35" s="53">
+        <v>91.028008929063319</v>
+      </c>
+      <c r="E35" s="53">
+        <v>89.101176850288709</v>
+      </c>
+      <c r="F35" s="53">
+        <v>84.121695311135312</v>
+      </c>
+      <c r="G35" s="53">
+        <v>75.514536359946376</v>
+      </c>
+      <c r="H35" s="53">
+        <v>58.551851548300363</v>
+      </c>
+      <c r="I35" s="54">
+        <v>43.528644478603361</v>
       </c>
       <c r="J35" s="50"/>
       <c r="K35" s="50"/>
       <c r="L35" s="1" t="str">
         <f t="shared" si="11"/>
-        <v xml:space="preserve">    92.8363134927282, 91.3590257907034, 89.6003860136814, 83.5494295124625, 75.4434513046841, 58.040988875657, 44.456943172035,</v>
-      </c>
-      <c r="M35" s="59" t="s">
+        <v xml:space="preserve">    92.6926858519851, 91.0280089290633, 89.1011768502887, 84.1216953111353, 75.5145363599464, 58.5518515483004, 43.5286444786034,</v>
+      </c>
+      <c r="M35" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="N35" s="60"/>
-      <c r="O35" s="34">
-        <v>4.0350169218649814</v>
-      </c>
-      <c r="P35" s="35">
-        <v>4.8715238888136483</v>
-      </c>
-      <c r="Q35" s="35">
-        <v>5.0114819755482234</v>
-      </c>
-      <c r="R35" s="35">
-        <v>5.5418311462698613</v>
-      </c>
-      <c r="S35" s="35">
-        <v>8.7209269933539382</v>
-      </c>
-      <c r="T35" s="35">
-        <v>10.65690967583773</v>
-      </c>
-      <c r="U35" s="36">
-        <v>11.553116561579911</v>
+      <c r="N35" s="66"/>
+      <c r="O35" s="52">
+        <v>4.3508377678439567</v>
+      </c>
+      <c r="P35" s="53">
+        <v>5.1455197984597092</v>
+      </c>
+      <c r="Q35" s="53">
+        <v>5.0319449257944937</v>
+      </c>
+      <c r="R35" s="53">
+        <v>5.4881092234662896</v>
+      </c>
+      <c r="S35" s="53">
+        <v>8.3963724907401343</v>
+      </c>
+      <c r="T35" s="53">
+        <v>11.26477476806841</v>
+      </c>
+      <c r="U35" s="54">
+        <v>10.478269846537319</v>
       </c>
       <c r="V35" s="1" t="str">
         <f t="shared" si="12"/>
-        <v xml:space="preserve">    4.03501692186498, 4.87152388881365, 5.01148197554822, 5.54183114626986, 8.72092699335394, 10.6569096758377, 11.5531165615799,</v>
+        <v xml:space="preserve">    4.35083776784396, 5.14551979845971, 5.03194492579449, 5.48810922346629, 8.39637249074013, 11.2647747680684, 10.4782698465373,</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="15" x14ac:dyDescent="0.2">
@@ -2965,54 +3001,6 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="A8:I8"/>
-    <mergeCell ref="M8:U8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="M13:U13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="A23:I23"/>
-    <mergeCell ref="M23:U23"/>
-    <mergeCell ref="A26:I26"/>
-    <mergeCell ref="M26:U26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="A31:I31"/>
-    <mergeCell ref="M31:U31"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="M35:N35"/>
     <mergeCell ref="A32:B32"/>
@@ -3021,10 +3009,58 @@
     <mergeCell ref="M33:N33"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="A31:I31"/>
+    <mergeCell ref="M31:U31"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="M26:U26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="M23:U23"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="A13:I13"/>
+    <mergeCell ref="M13:U13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="A8:I8"/>
+    <mergeCell ref="M8:U8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C9:I11 C6:I7 C2:I4">
-    <cfRule type="colorScale" priority="17">
+  <conditionalFormatting sqref="C6:I7 C2:I4">
+    <cfRule type="colorScale" priority="27">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3034,7 +3070,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="18">
+    <cfRule type="colorScale" priority="28">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3045,52 +3081,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:I11">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9:I12 C6:I7 C2:I4 C14:I17">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14:I16">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="9">
+  <conditionalFormatting sqref="C6:I7 C2:I4">
+    <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3114,7 +3106,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31:J35">
-    <cfRule type="colorScale" priority="4">
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3126,7 +3118,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:K17">
-    <cfRule type="colorScale" priority="239">
+    <cfRule type="colorScale" priority="249">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3138,7 +3130,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J5:K5 C3:K4">
-    <cfRule type="colorScale" priority="10">
+    <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3148,7 +3140,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="11">
+    <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3158,7 +3150,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="12">
+    <cfRule type="colorScale" priority="22">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3168,7 +3160,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="13">
+    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3178,7 +3170,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="14">
+    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3188,7 +3180,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="15">
+    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3199,8 +3191,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J12:K13 C2:K4 C6:K7 J5:K5 C9:K11 J8:K8 J17:K17 C14:K16">
-    <cfRule type="colorScale" priority="16">
+  <conditionalFormatting sqref="C2:K4 C6:K7 J5:K5 J8:K17">
+    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3212,7 +3204,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J31:K35">
-    <cfRule type="colorScale" priority="3">
+    <cfRule type="colorScale" priority="13">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3222,7 +3214,7 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="5">
+    <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3246,6 +3238,98 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K31:K35">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:I11">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:I11">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:I11">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:I12 C14:I17">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:I16">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:I11 C14:I16">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -3340,10 +3424,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="66"/>
+      <c r="B2" s="60"/>
       <c r="C2" s="20">
         <v>93.101364775358491</v>
       </c>
@@ -3377,10 +3461,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    93.1013647753585, 91.3266637254648, 89.7225610371485, 83.857204647099, 76.2429490451186, 60.4027774173364, 47.7409002961387,</v>
       </c>
-      <c r="M2" s="65" t="s">
+      <c r="M2" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="66"/>
+      <c r="N2" s="60"/>
       <c r="O2" s="37">
         <v>3.4649270444699574</v>
       </c>
@@ -3408,10 +3492,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="65" t="s">
+      <c r="A3" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="66"/>
+      <c r="B3" s="60"/>
       <c r="C3" s="37">
         <v>93.273358766079312</v>
       </c>
@@ -3445,10 +3529,10 @@
         <f t="shared" ref="L3:L16" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    93.2733587660793, 91.6155877934354, 90.6205330495939, 86.5975138193237, 78.2243502683126, 60.8549929786013, 48.7439337710534,</v>
       </c>
-      <c r="M3" s="65" t="s">
+      <c r="M3" s="59" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="66"/>
+      <c r="N3" s="60"/>
       <c r="O3" s="37">
         <v>3.4672469457762647</v>
       </c>
@@ -3476,10 +3560,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="65" t="s">
+      <c r="A4" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="66"/>
+      <c r="B4" s="60"/>
       <c r="C4" s="24">
         <v>87.593900000000005</v>
       </c>
@@ -3513,10 +3597,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    87.5939, 87.6637168141593, 88.1120943952802, 87.9700256922638, 87.4617081462642, 75.2513631894163, 47.7206838582802,</v>
       </c>
-      <c r="M4" s="65" t="s">
+      <c r="M4" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="66"/>
+      <c r="N4" s="60"/>
       <c r="O4" s="55">
         <v>2.4529187882918819</v>
       </c>
@@ -3544,31 +3628,31 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
-      <c r="D5" s="67"/>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="66"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="60"/>
       <c r="J5" s="41"/>
       <c r="K5" s="41"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="65" t="s">
+      <c r="M5" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="67"/>
-      <c r="S5" s="67"/>
-      <c r="T5" s="67"/>
-      <c r="U5" s="66"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
+      <c r="P5" s="61"/>
+      <c r="Q5" s="61"/>
+      <c r="R5" s="61"/>
+      <c r="S5" s="61"/>
+      <c r="T5" s="61"/>
+      <c r="U5" s="60"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -3984,590 +4068,590 @@
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="65" t="s">
+      <c r="A13" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="67"/>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="67"/>
-      <c r="F13" s="67"/>
-      <c r="G13" s="67"/>
-      <c r="H13" s="67"/>
-      <c r="I13" s="66"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="64"/>
+      <c r="D13" s="64"/>
+      <c r="E13" s="64"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="64"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="63"/>
       <c r="J13" s="41"/>
       <c r="K13" s="41"/>
       <c r="L13" s="12"/>
-      <c r="M13" s="65" t="s">
+      <c r="M13" s="59" t="s">
         <v>22</v>
       </c>
-      <c r="N13" s="67"/>
-      <c r="O13" s="67"/>
-      <c r="P13" s="67"/>
-      <c r="Q13" s="67"/>
-      <c r="R13" s="67"/>
-      <c r="S13" s="67"/>
-      <c r="T13" s="67"/>
-      <c r="U13" s="66"/>
+      <c r="N13" s="61"/>
+      <c r="O13" s="64"/>
+      <c r="P13" s="64"/>
+      <c r="Q13" s="64"/>
+      <c r="R13" s="64"/>
+      <c r="S13" s="64"/>
+      <c r="T13" s="64"/>
+      <c r="U13" s="63"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="65" t="s">
+      <c r="A14" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="55">
-        <v>93.32548436116808</v>
-      </c>
-      <c r="D14" s="32">
-        <v>92.739539269370866</v>
-      </c>
-      <c r="E14" s="32">
-        <v>91.500872268214565</v>
-      </c>
-      <c r="F14" s="32">
-        <v>85.143369175627228</v>
-      </c>
-      <c r="G14" s="32">
-        <v>75.147299428772442</v>
-      </c>
-      <c r="H14" s="32">
-        <v>59.129842530356363</v>
-      </c>
-      <c r="I14" s="33">
-        <v>48.364190001643621</v>
+      <c r="B14" s="60"/>
+      <c r="C14" s="75">
+        <v>93.782740335124032</v>
+      </c>
+      <c r="D14" s="76">
+        <v>91.948208894540599</v>
+      </c>
+      <c r="E14" s="76">
+        <v>90.212980504444957</v>
+      </c>
+      <c r="F14" s="76">
+        <v>84.630388959535409</v>
+      </c>
+      <c r="G14" s="76">
+        <v>75.371093175546491</v>
+      </c>
+      <c r="H14" s="76">
+        <v>59.627211308056303</v>
+      </c>
+      <c r="I14" s="77">
+        <v>47.844185503334799</v>
       </c>
       <c r="J14" s="41" cm="1">
         <f t="array" ref="J14">-SUMPRODUCT((D1:H1-C1:G1)*(C14:G14+D14:H14)/2)</f>
-        <v>78.680994068576155</v>
+        <v>78.220843605913544</v>
       </c>
       <c r="K14" s="41" cm="1">
         <f t="array" ref="K14">-SUMPRODUCT((D1:I1-C1:H1)*(C14:H14+D14:I14)/2)</f>
-        <v>81.368344881876155</v>
+        <v>80.907628526198323</v>
       </c>
       <c r="L14" s="12" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    93.3254843611681, 92.7395392693709, 91.5008722682146, 85.1433691756272, 75.1472994287724, 59.1298425303564, 48.3641900016436,</v>
-      </c>
-      <c r="M14" s="65" t="s">
+        <v xml:space="preserve">    93.782740335124, 91.9482088945406, 90.212980504445, 84.6303889595354, 75.3710931755465, 59.6272113080563, 47.8441855033348,</v>
+      </c>
+      <c r="M14" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="N14" s="66"/>
-      <c r="O14" s="55">
-        <v>3.667959563183556</v>
-      </c>
-      <c r="P14" s="32">
-        <v>3.989772059278164</v>
-      </c>
-      <c r="Q14" s="32">
-        <v>4.3227288020875694</v>
-      </c>
-      <c r="R14" s="32">
-        <v>4.691214264977404</v>
-      </c>
-      <c r="S14" s="32">
-        <v>9.351372365820513</v>
-      </c>
-      <c r="T14" s="32">
-        <v>11.12402361905577</v>
-      </c>
-      <c r="U14" s="33">
-        <v>9.7177921031411447</v>
+      <c r="N14" s="60"/>
+      <c r="O14" s="75">
+        <v>3.5391983918820551</v>
+      </c>
+      <c r="P14" s="76">
+        <v>4.1060038651541966</v>
+      </c>
+      <c r="Q14" s="76">
+        <v>4.774795806468676</v>
+      </c>
+      <c r="R14" s="76">
+        <v>5.3483339064680431</v>
+      </c>
+      <c r="S14" s="76">
+        <v>8.0994903921197494</v>
+      </c>
+      <c r="T14" s="76">
+        <v>10.59987402205407</v>
+      </c>
+      <c r="U14" s="77">
+        <v>8.7604668874903737</v>
       </c>
       <c r="V14" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    3.66795956318356, 3.98977205927816, 4.32272880208757, 4.6912142649774, 9.35137236582051, 11.1240236190558, 9.71779210314114,</v>
+        <v xml:space="preserve">    3.53919839188206, 4.1060038651542, 4.77479580646868, 5.34833390646804, 8.09949039211975, 10.5998740220541, 8.76046688749037,</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="70" t="s">
+      <c r="A15" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="69"/>
-      <c r="C15" s="55">
-        <v>93.029579263949799</v>
-      </c>
-      <c r="D15" s="32">
-        <v>91.699489903315182</v>
-      </c>
-      <c r="E15" s="32">
-        <v>90.230102913231647</v>
-      </c>
-      <c r="F15" s="32">
-        <v>85.684437869993104</v>
-      </c>
-      <c r="G15" s="32">
-        <v>76.604408342632709</v>
-      </c>
-      <c r="H15" s="32">
-        <v>60.525240991127369</v>
-      </c>
-      <c r="I15" s="33">
-        <v>50.546463781405251</v>
+      <c r="B15" s="63"/>
+      <c r="C15" s="78">
+        <v>93.226230330712227</v>
+      </c>
+      <c r="D15" s="79">
+        <v>91.83329152212967</v>
+      </c>
+      <c r="E15" s="79">
+        <v>90.325291164571794</v>
+      </c>
+      <c r="F15" s="79">
+        <v>85.383492360083878</v>
+      </c>
+      <c r="G15" s="79">
+        <v>76.567000291236639</v>
+      </c>
+      <c r="H15" s="79">
+        <v>59.41454222499042</v>
+      </c>
+      <c r="I15" s="80">
+        <v>50.563407411252108</v>
       </c>
       <c r="J15" s="41" cm="1">
         <f t="array" ref="J15">-SUMPRODUCT((D1:H1-C1:G1)*(C15:G15+D15:H15)/2)</f>
-        <v>78.394711603618248</v>
+        <v>78.369743178285859</v>
       </c>
       <c r="K15" s="41" cm="1">
         <f t="array" ref="K15">-SUMPRODUCT((D1:I1-C1:H1)*(C15:H15+D15:I15)/2)</f>
-        <v>81.17150422293156</v>
+        <v>81.11919191919192</v>
       </c>
       <c r="L15" s="12" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    93.0295792639498, 91.6994899033152, 90.2301029132316, 85.6844378699931, 76.6044083426327, 60.5252409911274, 50.5464637814053,</v>
-      </c>
-      <c r="M15" s="65" t="s">
+        <v xml:space="preserve">    93.2262303307122, 91.8332915221297, 90.3252911645718, 85.3834923600839, 76.5670002912366, 59.4145422249904, 50.5634074112521,</v>
+      </c>
+      <c r="M15" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="N15" s="66"/>
-      <c r="O15" s="55">
-        <v>3.744976414623296</v>
-      </c>
-      <c r="P15" s="32">
-        <v>4.343666270045687</v>
-      </c>
-      <c r="Q15" s="32">
-        <v>4.7437159565801874</v>
-      </c>
-      <c r="R15" s="32">
-        <v>5.5306123777224894</v>
-      </c>
-      <c r="S15" s="32">
-        <v>8.3512102986812558</v>
-      </c>
-      <c r="T15" s="32">
-        <v>10.38527872584435</v>
-      </c>
-      <c r="U15" s="33">
-        <v>9.5213328677383782</v>
+      <c r="N15" s="60"/>
+      <c r="O15" s="78">
+        <v>3.945711842949601</v>
+      </c>
+      <c r="P15" s="79">
+        <v>4.8525950161134093</v>
+      </c>
+      <c r="Q15" s="79">
+        <v>4.4346894499148144</v>
+      </c>
+      <c r="R15" s="79">
+        <v>5.4810029574676529</v>
+      </c>
+      <c r="S15" s="79">
+        <v>8.4636725644600066</v>
+      </c>
+      <c r="T15" s="79">
+        <v>10.788297692871961</v>
+      </c>
+      <c r="U15" s="80">
+        <v>8.7433484877826491</v>
       </c>
       <c r="V15" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    3.7449764146233, 4.34366627004569, 4.74371595658019, 5.53061237772249, 8.35121029868126, 10.3852787258443, 9.52133286773838,</v>
+        <v xml:space="preserve">    3.9457118429496, 4.85259501611341, 4.43468944991481, 5.48100295746765, 8.46367256446001, 10.788297692872, 8.74334848778265,</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="65" t="s">
+      <c r="A16" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="55">
-        <v>92.961657684466715</v>
-      </c>
-      <c r="D16" s="32">
-        <v>91.581357393518388</v>
-      </c>
-      <c r="E16" s="32">
-        <v>90.473438351542839</v>
-      </c>
-      <c r="F16" s="32">
-        <v>86.603606720934735</v>
-      </c>
-      <c r="G16" s="32">
-        <v>77.903932271617123</v>
-      </c>
-      <c r="H16" s="32">
-        <v>59.567908603592286</v>
-      </c>
-      <c r="I16" s="33">
-        <v>48.445153793141223</v>
+      <c r="B16" s="60"/>
+      <c r="C16" s="78">
+        <v>93.004922187908207</v>
+      </c>
+      <c r="D16" s="79">
+        <v>91.518502178507859</v>
+      </c>
+      <c r="E16" s="79">
+        <v>89.729420958082102</v>
+      </c>
+      <c r="F16" s="79">
+        <v>83.348607398564567</v>
+      </c>
+      <c r="G16" s="79">
+        <v>74.087719905304837</v>
+      </c>
+      <c r="H16" s="79">
+        <v>57.917332041511322</v>
+      </c>
+      <c r="I16" s="80">
+        <v>48.007794185070807</v>
       </c>
       <c r="J16" s="41" cm="1">
         <f t="array" ref="J16">-SUMPRODUCT((D1:H1-C1:G1)*(C16:G16+D16:H16)/2)</f>
-        <v>78.631399853516598</v>
+        <v>77.501290236074709</v>
       </c>
       <c r="K16" s="41" cm="1">
         <f t="array" ref="K16">-SUMPRODUCT((D1:I1-C1:H1)*(C16:H16+D16:I16)/2)</f>
-        <v>81.331726413434936</v>
+        <v>80.14941839173926</v>
       </c>
       <c r="L16" s="12" t="str">
         <f t="shared" si="0"/>
-        <v xml:space="preserve">    92.9616576844667, 91.5813573935184, 90.4734383515428, 86.6036067209347, 77.9039322716171, 59.5679086035923, 48.4451537931412,</v>
-      </c>
-      <c r="M16" s="65" t="s">
+        <v xml:space="preserve">    93.0049221879082, 91.5185021785079, 89.7294209580821, 83.3486073985646, 74.0877199053048, 57.9173320415113, 48.0077941850708,</v>
+      </c>
+      <c r="M16" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="N16" s="66"/>
-      <c r="O16" s="43">
-        <v>3.561541743303076</v>
-      </c>
-      <c r="P16" s="44">
-        <v>4.0732299909545224</v>
-      </c>
-      <c r="Q16" s="44">
-        <v>4.7078541322877587</v>
-      </c>
-      <c r="R16" s="44">
-        <v>5.7340237026421512</v>
-      </c>
-      <c r="S16" s="44">
-        <v>7.7315701222211866</v>
-      </c>
-      <c r="T16" s="44">
-        <v>8.7921119837631458</v>
-      </c>
-      <c r="U16" s="45">
-        <v>6.9480359155607783</v>
+      <c r="N16" s="60"/>
+      <c r="O16" s="78">
+        <v>3.690401528555848</v>
+      </c>
+      <c r="P16" s="79">
+        <v>4.2469367469027457</v>
+      </c>
+      <c r="Q16" s="79">
+        <v>4.4611096369834957</v>
+      </c>
+      <c r="R16" s="79">
+        <v>5.4089286426803449</v>
+      </c>
+      <c r="S16" s="79">
+        <v>9.092124974067179</v>
+      </c>
+      <c r="T16" s="79">
+        <v>10.83557708581068</v>
+      </c>
+      <c r="U16" s="80">
+        <v>9.2904800440053528</v>
       </c>
       <c r="V16" s="12" t="str">
         <f t="shared" si="1"/>
-        <v xml:space="preserve">    3.56154174330308, 4.07322999095452, 4.70785413228776, 5.73402370264215, 7.73157012222119, 8.79211198376315, 6.94803591556078,</v>
+        <v xml:space="preserve">    3.69040152855585, 4.24693674690275, 4.4611096369835, 5.40892864268034, 9.09212497406718, 10.8355770858107, 9.29048004400535,</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="65" t="s">
+      <c r="A17" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="66"/>
-      <c r="C17" s="55">
-        <v>93.033472031188253</v>
-      </c>
-      <c r="D17" s="32">
-        <v>91.100681378443298</v>
-      </c>
-      <c r="E17" s="32">
-        <v>89.756246449652096</v>
-      </c>
-      <c r="F17" s="32">
-        <v>83.92601147068747</v>
-      </c>
-      <c r="G17" s="32">
-        <v>76.162322626781645</v>
-      </c>
-      <c r="H17" s="32">
-        <v>59.765018151829473</v>
-      </c>
-      <c r="I17" s="33">
-        <v>48.291320282470707</v>
+      <c r="B17" s="60"/>
+      <c r="C17" s="81">
+        <v>93.123279613145442</v>
+      </c>
+      <c r="D17" s="82">
+        <v>91.674385879923975</v>
+      </c>
+      <c r="E17" s="82">
+        <v>89.698688281617194</v>
+      </c>
+      <c r="F17" s="82">
+        <v>84.957067102656595</v>
+      </c>
+      <c r="G17" s="82">
+        <v>75.939082518014857</v>
+      </c>
+      <c r="H17" s="82">
+        <v>59.995092229748238</v>
+      </c>
+      <c r="I17" s="83">
+        <v>48.440303693515233</v>
       </c>
       <c r="J17" s="41" cm="1">
         <f t="array" ref="J17">-SUMPRODUCT((D1:H1-C1:G1)*(C17:G17+D17:H17)/2)</f>
-        <v>77.792894690553823</v>
+        <v>78.078434213675436</v>
       </c>
       <c r="K17" s="41" cm="1">
         <f t="array" ref="K17">-SUMPRODUCT((D1:I1-C1:H1)*(C17:H17+D17:I17)/2)</f>
-        <v>80.49430315141133</v>
+        <v>80.789319111757024</v>
       </c>
       <c r="L17" s="12"/>
-      <c r="M17" s="65" t="s">
+      <c r="M17" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="N17" s="66"/>
-      <c r="O17" s="55">
-        <v>3.8568466007702029</v>
-      </c>
-      <c r="P17" s="32">
-        <v>4.6595572983107783</v>
-      </c>
-      <c r="Q17" s="32">
-        <v>4.7370792660764716</v>
-      </c>
-      <c r="R17" s="32">
-        <v>5.5210922070370687</v>
-      </c>
-      <c r="S17" s="32">
-        <v>8.0424472924959218</v>
-      </c>
-      <c r="T17" s="32">
-        <v>10.57495823817662</v>
-      </c>
-      <c r="U17" s="33">
-        <v>9.4501253063826809</v>
+      <c r="N17" s="60"/>
+      <c r="O17" s="81">
+        <v>3.8088682011350912</v>
+      </c>
+      <c r="P17" s="82">
+        <v>4.4783864386850611</v>
+      </c>
+      <c r="Q17" s="82">
+        <v>5.0849840192173117</v>
+      </c>
+      <c r="R17" s="82">
+        <v>5.0366327026230584</v>
+      </c>
+      <c r="S17" s="82">
+        <v>7.6643798786674449</v>
+      </c>
+      <c r="T17" s="82">
+        <v>10.05146904627655</v>
+      </c>
+      <c r="U17" s="83">
+        <v>9.821397671709315</v>
       </c>
       <c r="V17" s="12"/>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="65" t="s">
+      <c r="A18" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="67"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="68"/>
-      <c r="I18" s="69"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="74"/>
       <c r="J18" s="41"/>
       <c r="K18" s="41"/>
       <c r="L18" s="12"/>
-      <c r="M18" s="65" t="s">
+      <c r="M18" s="59" t="s">
         <v>25</v>
       </c>
-      <c r="N18" s="67"/>
-      <c r="O18" s="68"/>
-      <c r="P18" s="68"/>
-      <c r="Q18" s="68"/>
-      <c r="R18" s="68"/>
-      <c r="S18" s="68"/>
-      <c r="T18" s="68"/>
-      <c r="U18" s="69"/>
+      <c r="N18" s="61"/>
+      <c r="O18" s="73"/>
+      <c r="P18" s="73"/>
+      <c r="Q18" s="73"/>
+      <c r="R18" s="73"/>
+      <c r="S18" s="73"/>
+      <c r="T18" s="73"/>
+      <c r="U18" s="74"/>
       <c r="V18" s="12"/>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="65" t="s">
+      <c r="A19" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="66"/>
-      <c r="C19" s="55">
-        <v>91.808259587020672</v>
-      </c>
-      <c r="D19" s="32">
-        <v>90.918387413962634</v>
-      </c>
-      <c r="E19" s="32">
-        <v>89.996141835136996</v>
-      </c>
-      <c r="F19" s="32">
-        <v>87.690311623226279</v>
-      </c>
-      <c r="G19" s="32">
-        <v>84.300178490586703</v>
-      </c>
-      <c r="H19" s="32">
-        <v>60.212671966597178</v>
-      </c>
-      <c r="I19" s="33">
-        <v>42.728460742163293</v>
+      <c r="B19" s="60"/>
+      <c r="C19" s="75">
+        <v>92.969518190757128</v>
+      </c>
+      <c r="D19" s="76">
+        <v>91.851524090462149</v>
+      </c>
+      <c r="E19" s="76">
+        <v>90.756145526057011</v>
+      </c>
+      <c r="F19" s="76">
+        <v>87.253136561158271</v>
+      </c>
+      <c r="G19" s="76">
+        <v>81.178972136437139</v>
+      </c>
+      <c r="H19" s="76">
+        <v>57.386929529378847</v>
+      </c>
+      <c r="I19" s="77">
+        <v>44.855442809482213</v>
       </c>
       <c r="J19" s="41" cm="1">
         <f t="array" ref="J19">-SUMPRODUCT((D1:H1-C1:G1)*(C19:G19+D19:H19)/2)</f>
-        <v>79.048959405646542</v>
+        <v>79.079417714109411</v>
       </c>
       <c r="K19" s="41" cm="1">
         <f t="array" ref="K19">-SUMPRODUCT((D1:I1-C1:H1)*(C19:H19+D19:I19)/2)</f>
-        <v>81.622487723365552</v>
+        <v>81.635477022580943</v>
       </c>
       <c r="L19" s="12" t="str">
         <f t="shared" ref="L19:L21" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C19:I19)&amp;","</f>
-        <v xml:space="preserve">    91.8082595870207, 90.9183874139626, 89.996141835137, 87.6903116232263, 84.3001784905867, 60.2126719665972, 42.7284607421633,</v>
-      </c>
-      <c r="M19" s="65" t="s">
+        <v xml:space="preserve">    92.9695181907571, 91.8515240904621, 90.756145526057, 87.2531365611583, 81.1789721364371, 57.3869295293788, 44.8554428094822,</v>
+      </c>
+      <c r="M19" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="N19" s="66"/>
-      <c r="O19" s="55">
-        <v>3.5081436422345762</v>
-      </c>
-      <c r="P19" s="32">
-        <v>3.2318299507081201</v>
-      </c>
-      <c r="Q19" s="32">
-        <v>2.9043906528931069</v>
-      </c>
-      <c r="R19" s="32">
-        <v>3.2703414364377852</v>
-      </c>
-      <c r="S19" s="32">
-        <v>3.862191195058998</v>
-      </c>
-      <c r="T19" s="32">
-        <v>7.0362299825413483</v>
-      </c>
-      <c r="U19" s="33">
-        <v>3.4420784039601222</v>
+      <c r="N19" s="60"/>
+      <c r="O19" s="75">
+        <v>3.3991921823554931</v>
+      </c>
+      <c r="P19" s="76">
+        <v>3.6561489783789969</v>
+      </c>
+      <c r="Q19" s="76">
+        <v>3.4316179388806831</v>
+      </c>
+      <c r="R19" s="76">
+        <v>3.3610781227617821</v>
+      </c>
+      <c r="S19" s="76">
+        <v>5.2773835873092807</v>
+      </c>
+      <c r="T19" s="76">
+        <v>8.2027130196510409</v>
+      </c>
+      <c r="U19" s="77">
+        <v>5.203571843512913</v>
       </c>
       <c r="V19" s="12" t="str">
         <f t="shared" ref="V19:V21" si="3">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O19:U19)&amp;","</f>
-        <v xml:space="preserve">    3.50814364223458, 3.23182995070812, 2.90439065289311, 3.27034143643779, 3.862191195059, 7.03622998254135, 3.44207840396012,</v>
+        <v xml:space="preserve">    3.39919218235549, 3.656148978379, 3.43161793888068, 3.36107812276178, 5.27738358730928, 8.20271301965104, 5.20357184351291,</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="70" t="s">
+      <c r="A20" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="69"/>
-      <c r="C20" s="55">
-        <v>91.806402592871336</v>
-      </c>
-      <c r="D20" s="32">
-        <v>91.000000000000014</v>
-      </c>
-      <c r="E20" s="32">
-        <v>89.899705014749259</v>
-      </c>
-      <c r="F20" s="32">
-        <v>87.81909301406877</v>
-      </c>
-      <c r="G20" s="32">
-        <v>85.468643039011297</v>
-      </c>
-      <c r="H20" s="32">
-        <v>70.467985593877685</v>
-      </c>
-      <c r="I20" s="33">
-        <v>45.777178003269917</v>
+      <c r="B20" s="63"/>
+      <c r="C20" s="78">
+        <v>91.898721730580135</v>
+      </c>
+      <c r="D20" s="79">
+        <v>90.765995668936</v>
+      </c>
+      <c r="E20" s="79">
+        <v>89.705268500015848</v>
+      </c>
+      <c r="F20" s="79">
+        <v>87.959685349065893</v>
+      </c>
+      <c r="G20" s="79">
+        <v>85.750000720882824</v>
+      </c>
+      <c r="H20" s="79">
+        <v>71.387388010853613</v>
+      </c>
+      <c r="I20" s="80">
+        <v>45.596343105620853</v>
       </c>
       <c r="J20" s="41" cm="1">
         <f t="array" ref="J20">-SUMPRODUCT((D1:H1-C1:G1)*(C20:G20+D20:H20)/2)</f>
-        <v>79.696361488132837</v>
+        <v>79.700846821050931</v>
       </c>
       <c r="K20" s="41" cm="1">
         <f t="array" ref="K20">-SUMPRODUCT((D1:I1-C1:H1)*(C20:H20+D20:I20)/2)</f>
-        <v>82.60249057806152</v>
+        <v>82.625440098962798</v>
       </c>
       <c r="L20" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    91.8064025928713, 91, 89.8997050147493, 87.8190930140688, 85.4686430390113, 70.4679855938777, 45.7771780032699,</v>
-      </c>
-      <c r="M20" s="65" t="s">
+        <v xml:space="preserve">    91.8987217305801, 90.765995668936, 89.7052685000158, 87.9596853490659, 85.7500007208828, 71.3873880108536, 45.5963431056209,</v>
+      </c>
+      <c r="M20" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="N20" s="66"/>
-      <c r="O20" s="55">
-        <v>3.30162613426437</v>
-      </c>
-      <c r="P20" s="32">
-        <v>2.7895411419086922</v>
-      </c>
-      <c r="Q20" s="32">
-        <v>2.4165108199523742</v>
-      </c>
-      <c r="R20" s="32">
-        <v>2.7123736733211721</v>
-      </c>
-      <c r="S20" s="32">
-        <v>3.8014726287512541</v>
-      </c>
-      <c r="T20" s="32">
-        <v>5.2299009938051402</v>
-      </c>
-      <c r="U20" s="33">
-        <v>2.1746822737589162</v>
+      <c r="N20" s="60"/>
+      <c r="O20" s="78">
+        <v>3.190312271555559</v>
+      </c>
+      <c r="P20" s="79">
+        <v>2.8828036064622768</v>
+      </c>
+      <c r="Q20" s="79">
+        <v>2.5884740771146331</v>
+      </c>
+      <c r="R20" s="79">
+        <v>2.6213450470877251</v>
+      </c>
+      <c r="S20" s="79">
+        <v>3.203569989687661</v>
+      </c>
+      <c r="T20" s="79">
+        <v>4.756712112750666</v>
+      </c>
+      <c r="U20" s="80">
+        <v>2.488810891584841</v>
       </c>
       <c r="V20" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    3.30162613426437, 2.78954114190869, 2.41651081995237, 2.71237367332117, 3.80147262875125, 5.22990099380514, 2.17468227375892,</v>
+        <v xml:space="preserve">    3.19031227155556, 2.88280360646228, 2.58847407711463, 2.62134504708773, 3.20356998968766, 4.75671211275067, 2.48881089158484,</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="65" t="s">
+      <c r="A21" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="66"/>
-      <c r="C21" s="55">
-        <v>93.12979927738705</v>
-      </c>
-      <c r="D21" s="32">
-        <v>92.072884136829316</v>
-      </c>
-      <c r="E21" s="32">
-        <v>90.991179277790764</v>
-      </c>
-      <c r="F21" s="32">
-        <v>86.488871010994899</v>
-      </c>
-      <c r="G21" s="32">
-        <v>78.849479666779118</v>
-      </c>
-      <c r="H21" s="32">
-        <v>59.403051352808703</v>
-      </c>
-      <c r="I21" s="33">
-        <v>48.981470427944863</v>
+      <c r="B21" s="60"/>
+      <c r="C21" s="78">
+        <v>93.044276622923505</v>
+      </c>
+      <c r="D21" s="79">
+        <v>91.935155148400938</v>
+      </c>
+      <c r="E21" s="79">
+        <v>90.94889229145582</v>
+      </c>
+      <c r="F21" s="79">
+        <v>85.952505356159378</v>
+      </c>
+      <c r="G21" s="79">
+        <v>78.915183810701947</v>
+      </c>
+      <c r="H21" s="79">
+        <v>59.442100133507502</v>
+      </c>
+      <c r="I21" s="80">
+        <v>49.533828147302302</v>
       </c>
       <c r="J21" s="41" cm="1">
         <f t="array" ref="J21">-SUMPRODUCT((D1:H1-C1:G1)*(C21:G21+D21:H21)/2)</f>
-        <v>78.960892467351215</v>
+        <v>78.834323321712716</v>
       </c>
       <c r="K21" s="41" cm="1">
         <f t="array" ref="K21">-SUMPRODUCT((D1:I1-C1:H1)*(C21:H21+D21:I21)/2)</f>
-        <v>81.670505511870061</v>
+        <v>81.55872152873296</v>
       </c>
       <c r="L21" s="12" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve">    93.1297992773871, 92.0728841368293, 90.9911792777908, 86.4888710109949, 78.8494796667791, 59.4030513528087, 48.9814704279449,</v>
-      </c>
-      <c r="M21" s="65" t="s">
+        <v xml:space="preserve">    93.0442766229235, 91.9351551484009, 90.9488922914558, 85.9525053561594, 78.9151838107019, 59.4421001335075, 49.5338281473023,</v>
+      </c>
+      <c r="M21" s="59" t="s">
         <v>23</v>
       </c>
-      <c r="N21" s="66"/>
-      <c r="O21" s="55">
-        <v>3.720535922449947</v>
-      </c>
-      <c r="P21" s="32">
-        <v>4.0622972018703303</v>
-      </c>
-      <c r="Q21" s="32">
-        <v>3.8973921609932098</v>
-      </c>
-      <c r="R21" s="32">
-        <v>4.4056182294833066</v>
-      </c>
-      <c r="S21" s="32">
-        <v>6.8043189964443149</v>
-      </c>
-      <c r="T21" s="32">
-        <v>10.63228683456753</v>
-      </c>
-      <c r="U21" s="33">
-        <v>8.6293638993197188</v>
+      <c r="N21" s="60"/>
+      <c r="O21" s="78">
+        <v>3.72078192123604</v>
+      </c>
+      <c r="P21" s="79">
+        <v>4.0467152776216686</v>
+      </c>
+      <c r="Q21" s="79">
+        <v>4.0235763627769954</v>
+      </c>
+      <c r="R21" s="79">
+        <v>4.4767633212331157</v>
+      </c>
+      <c r="S21" s="79">
+        <v>7.2019016527503927</v>
+      </c>
+      <c r="T21" s="79">
+        <v>10.04668436860082</v>
+      </c>
+      <c r="U21" s="80">
+        <v>9.2355901481835172</v>
       </c>
       <c r="V21" s="12" t="str">
         <f t="shared" si="3"/>
-        <v xml:space="preserve">    3.72053592244995, 4.06229720187033, 3.89739216099321, 4.40561822948331, 6.80431899644431, 10.6322868345675, 8.62936389931972,</v>
+        <v xml:space="preserve">    3.72078192123604, 4.04671527762167, 4.023576362777, 4.47676332123312, 7.20190165275039, 10.0466843686008, 9.23559014818352,</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="65" t="s">
+      <c r="A22" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="66"/>
-      <c r="C22" s="55">
-        <v>93.29405963719411</v>
-      </c>
-      <c r="D22" s="32">
-        <v>91.739729582435828</v>
-      </c>
-      <c r="E22" s="32">
-        <v>90.005885287358296</v>
-      </c>
-      <c r="F22" s="32">
-        <v>84.180898335337389</v>
-      </c>
-      <c r="G22" s="32">
-        <v>76.342811500676177</v>
-      </c>
-      <c r="H22" s="32">
-        <v>59.562899909745468</v>
-      </c>
-      <c r="I22" s="33">
-        <v>48.344573338293003</v>
+      <c r="B22" s="60"/>
+      <c r="C22" s="81">
+        <v>93.174110502686005</v>
+      </c>
+      <c r="D22" s="82">
+        <v>91.391724841910417</v>
+      </c>
+      <c r="E22" s="82">
+        <v>89.591539142495463</v>
+      </c>
+      <c r="F22" s="82">
+        <v>84.690597092823751</v>
+      </c>
+      <c r="G22" s="82">
+        <v>76.401347185817656</v>
+      </c>
+      <c r="H22" s="82">
+        <v>59.963667505774268</v>
+      </c>
+      <c r="I22" s="83">
+        <v>47.725577210875521</v>
       </c>
       <c r="J22" s="41" cm="1">
         <f t="array" ref="J22">-SUMPRODUCT((D1:H1-C1:G1)*(C22:G22+D22:H22)/2)</f>
-        <v>78.087574935769339</v>
+        <v>77.994698988168864</v>
       </c>
       <c r="K22" s="41" cm="1">
         <f t="array" ref="K22">-SUMPRODUCT((D1:I1-C1:H1)*(C22:H22+D22:I22)/2)</f>
-        <v>80.785261766970308</v>
+        <v>80.686930106085114</v>
       </c>
       <c r="L22" s="12"/>
-      <c r="M22" s="65" t="s">
+      <c r="M22" s="59" t="s">
         <v>24</v>
       </c>
-      <c r="N22" s="66"/>
-      <c r="O22" s="55">
-        <v>3.5976530252225301</v>
-      </c>
-      <c r="P22" s="32">
-        <v>4.5356023728221411</v>
-      </c>
-      <c r="Q22" s="32">
-        <v>4.6296560466546204</v>
-      </c>
-      <c r="R22" s="32">
-        <v>5.2864726273441152</v>
-      </c>
-      <c r="S22" s="32">
-        <v>8.2846675717539657</v>
-      </c>
-      <c r="T22" s="32">
-        <v>10.25067270866937</v>
-      </c>
-      <c r="U22" s="33">
-        <v>9.5941688433330885</v>
+      <c r="N22" s="60"/>
+      <c r="O22" s="81">
+        <v>3.8766021792735019</v>
+      </c>
+      <c r="P22" s="82">
+        <v>4.8126411406228078</v>
+      </c>
+      <c r="Q22" s="82">
+        <v>4.6512210016047986</v>
+      </c>
+      <c r="R22" s="82">
+        <v>5.2416066355763284</v>
+      </c>
+      <c r="S22" s="82">
+        <v>8.0769588602235256</v>
+      </c>
+      <c r="T22" s="82">
+        <v>10.657363307561541</v>
+      </c>
+      <c r="U22" s="83">
+        <v>9.200486032966916</v>
       </c>
       <c r="V22" s="12"/>
     </row>
@@ -4654,10 +4738,10 @@
       <c r="V24" s="1"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="59" t="s">
+      <c r="A25" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="60"/>
+      <c r="B25" s="66"/>
       <c r="C25" s="47">
         <v>92.567111769713335</v>
       </c>
@@ -4685,10 +4769,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C25:I25)&amp;","</f>
         <v xml:space="preserve">    92.5671117697133, 90.8358586083436, 89.2175053395332, 83.2372459642881, 75.380430844191, 58.9943671875974, 43.6225356413822,</v>
       </c>
-      <c r="M25" s="59" t="s">
+      <c r="M25" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="N25" s="60"/>
+      <c r="N25" s="66"/>
       <c r="O25" s="46">
         <v>3.88093621561358</v>
       </c>
@@ -4716,10 +4800,10 @@
       </c>
     </row>
     <row r="26" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="59" t="s">
+      <c r="A26" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="60"/>
+      <c r="B26" s="66"/>
       <c r="C26" s="47">
         <v>92.866950218042462</v>
       </c>
@@ -4747,10 +4831,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
         <v xml:space="preserve">    92.8669502180425, 91.2426907647456, 90.1370532276984, 86.0801529266134, 77.4102172551968, 59.6761947649801, 46.3954904194042,</v>
       </c>
-      <c r="M26" s="59" t="s">
+      <c r="M26" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="N26" s="60"/>
+      <c r="N26" s="66"/>
       <c r="O26" s="47">
         <v>3.8319643020864191</v>
       </c>
@@ -4778,10 +4862,10 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="59" t="s">
+      <c r="A27" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="B27" s="60"/>
+      <c r="B27" s="66"/>
       <c r="C27" s="34">
         <v>87.268396410214976</v>
       </c>
@@ -4809,10 +4893,10 @@
         <f t="shared" ref="L27:L35" si="5">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:I27)&amp;","</f>
         <v xml:space="preserve">    87.268396410215, 87.2564283986868, 87.8221063041704, 87.6807264423516, 87.1448793671852, 74.9765678865158, 46.4175473948824,</v>
       </c>
-      <c r="M27" s="59" t="s">
+      <c r="M27" s="65" t="s">
         <v>10</v>
       </c>
-      <c r="N27" s="60"/>
+      <c r="N27" s="66"/>
       <c r="O27" s="34">
         <v>2.610595868561878</v>
       </c>
@@ -4840,31 +4924,31 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="59" t="s">
+      <c r="A28" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="B28" s="63"/>
-      <c r="C28" s="63"/>
-      <c r="D28" s="63"/>
-      <c r="E28" s="63"/>
-      <c r="F28" s="63"/>
-      <c r="G28" s="63"/>
-      <c r="H28" s="63"/>
-      <c r="I28" s="60"/>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="67"/>
+      <c r="G28" s="67"/>
+      <c r="H28" s="67"/>
+      <c r="I28" s="66"/>
       <c r="J28" s="50"/>
       <c r="K28" s="50"/>
       <c r="L28" s="1"/>
-      <c r="M28" s="59" t="s">
+      <c r="M28" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="N28" s="63"/>
-      <c r="O28" s="63"/>
-      <c r="P28" s="63"/>
-      <c r="Q28" s="63"/>
-      <c r="R28" s="63"/>
-      <c r="S28" s="63"/>
-      <c r="T28" s="63"/>
-      <c r="U28" s="60"/>
+      <c r="N28" s="67"/>
+      <c r="O28" s="67"/>
+      <c r="P28" s="67"/>
+      <c r="Q28" s="67"/>
+      <c r="R28" s="67"/>
+      <c r="S28" s="67"/>
+      <c r="T28" s="67"/>
+      <c r="U28" s="66"/>
       <c r="V28" s="1"/>
     </row>
     <row r="29" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -5250,542 +5334,542 @@
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="59" t="s">
+      <c r="A36" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="B36" s="63"/>
-      <c r="C36" s="63"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="63"/>
-      <c r="F36" s="63"/>
-      <c r="G36" s="63"/>
-      <c r="H36" s="63"/>
-      <c r="I36" s="60"/>
+      <c r="B36" s="67"/>
+      <c r="C36" s="68"/>
+      <c r="D36" s="68"/>
+      <c r="E36" s="68"/>
+      <c r="F36" s="68"/>
+      <c r="G36" s="68"/>
+      <c r="H36" s="68"/>
+      <c r="I36" s="69"/>
       <c r="J36" s="50"/>
       <c r="K36" s="50"/>
       <c r="L36" s="1"/>
-      <c r="M36" s="59" t="s">
+      <c r="M36" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="N36" s="63"/>
-      <c r="O36" s="63"/>
-      <c r="P36" s="63"/>
-      <c r="Q36" s="63"/>
-      <c r="R36" s="63"/>
-      <c r="S36" s="63"/>
-      <c r="T36" s="63"/>
-      <c r="U36" s="60"/>
+      <c r="N36" s="67"/>
+      <c r="O36" s="68"/>
+      <c r="P36" s="68"/>
+      <c r="Q36" s="68"/>
+      <c r="R36" s="68"/>
+      <c r="S36" s="68"/>
+      <c r="T36" s="68"/>
+      <c r="U36" s="69"/>
       <c r="V36" s="1"/>
     </row>
     <row r="37" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="59" t="s">
+      <c r="A37" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="B37" s="60"/>
-      <c r="C37" s="34">
-        <v>92.868050634154315</v>
-      </c>
-      <c r="D37" s="35">
-        <v>92.288231222045297</v>
-      </c>
-      <c r="E37" s="35">
-        <v>91.054287148035144</v>
-      </c>
-      <c r="F37" s="35">
-        <v>84.437885333085376</v>
-      </c>
-      <c r="G37" s="35">
-        <v>74.253673383599548</v>
-      </c>
-      <c r="H37" s="35">
-        <v>57.552195558991649</v>
-      </c>
-      <c r="I37" s="36">
-        <v>45.560977654736433</v>
+      <c r="B37" s="66"/>
+      <c r="C37" s="84">
+        <v>93.403798109785029</v>
+      </c>
+      <c r="D37" s="85">
+        <v>91.51700700493744</v>
+      </c>
+      <c r="E37" s="85">
+        <v>89.749880462689262</v>
+      </c>
+      <c r="F37" s="85">
+        <v>83.99730958119234</v>
+      </c>
+      <c r="G37" s="85">
+        <v>74.394962965986878</v>
+      </c>
+      <c r="H37" s="85">
+        <v>58.095582470498513</v>
+      </c>
+      <c r="I37" s="86">
+        <v>44.434812706207254</v>
       </c>
       <c r="J37" s="50"/>
       <c r="K37" s="50"/>
       <c r="L37" s="1" t="str">
         <f t="shared" ref="L37:L39" si="6">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C37:I37)&amp;","</f>
-        <v xml:space="preserve">    92.8680506341543, 92.2882312220453, 91.0542871480351, 84.4378853330854, 74.2536733835995, 57.5521955589916, 45.5609776547364,</v>
-      </c>
-      <c r="M37" s="59" t="s">
+        <v xml:space="preserve">    93.403798109785, 91.5170070049374, 89.7498804626893, 83.9973095811923, 74.3949629659869, 58.0955824704985, 44.4348127062073,</v>
+      </c>
+      <c r="M37" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="N37" s="60"/>
-      <c r="O37" s="34">
-        <v>4.0949495507503526</v>
-      </c>
-      <c r="P37" s="35">
-        <v>4.4354851591423481</v>
-      </c>
-      <c r="Q37" s="35">
-        <v>4.6437372111598876</v>
-      </c>
-      <c r="R37" s="35">
-        <v>5.0311660763107948</v>
-      </c>
-      <c r="S37" s="35">
-        <v>9.8512038160577102</v>
-      </c>
-      <c r="T37" s="35">
-        <v>11.57485796488027</v>
-      </c>
-      <c r="U37" s="36">
-        <v>10.571075661324681</v>
+      <c r="N37" s="66"/>
+      <c r="O37" s="84">
+        <v>3.9553866501853321</v>
+      </c>
+      <c r="P37" s="85">
+        <v>4.517630835861226</v>
+      </c>
+      <c r="Q37" s="85">
+        <v>5.2125425794506972</v>
+      </c>
+      <c r="R37" s="85">
+        <v>5.6477461387684551</v>
+      </c>
+      <c r="S37" s="85">
+        <v>8.6090564713117175</v>
+      </c>
+      <c r="T37" s="85">
+        <v>11.357157347254571</v>
+      </c>
+      <c r="U37" s="86">
+        <v>9.3757621724255777</v>
       </c>
       <c r="V37" s="1" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    4.09494955075035, 4.43548515914235, 4.64373721115989, 5.03116607631079, 9.85120381605771, 11.5748579648803, 10.5710756613247,</v>
+        <v xml:space="preserve">    3.95538665018533, 4.51763083586123, 5.2125425794507, 5.64774613876846, 8.60905647131172, 11.3571573472546, 9.37576217242558,</v>
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="59" t="s">
+      <c r="A38" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="B38" s="60"/>
-      <c r="C38" s="34">
-        <v>92.513598322189821</v>
-      </c>
-      <c r="D38" s="35">
-        <v>91.261446870594469</v>
-      </c>
-      <c r="E38" s="35">
-        <v>89.758265941661861</v>
-      </c>
-      <c r="F38" s="35">
-        <v>85.044465656129674</v>
-      </c>
-      <c r="G38" s="35">
-        <v>75.898843968080286</v>
-      </c>
-      <c r="H38" s="35">
-        <v>59.465611837116732</v>
-      </c>
-      <c r="I38" s="36">
-        <v>48.473156490254198</v>
+      <c r="B38" s="66"/>
+      <c r="C38" s="87">
+        <v>92.778947400409621</v>
+      </c>
+      <c r="D38" s="88">
+        <v>91.450368996373655</v>
+      </c>
+      <c r="E38" s="88">
+        <v>89.879480954542075</v>
+      </c>
+      <c r="F38" s="88">
+        <v>84.748756470336986</v>
+      </c>
+      <c r="G38" s="88">
+        <v>75.627608782580538</v>
+      </c>
+      <c r="H38" s="88">
+        <v>58.300265665116903</v>
+      </c>
+      <c r="I38" s="89">
+        <v>48.584106437626268</v>
       </c>
       <c r="J38" s="50"/>
       <c r="K38" s="50"/>
       <c r="L38" s="1" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    92.5135983221898, 91.2614468705945, 89.7582659416619, 85.0444656561297, 75.8988439680803, 59.4656118371167, 48.4731564902542,</v>
-      </c>
-      <c r="M38" s="59" t="s">
+        <v xml:space="preserve">    92.7789474004096, 91.4503689963737, 89.8794809545421, 84.748756470337, 75.6276087825805, 58.3002656651169, 48.5841064376263,</v>
+      </c>
+      <c r="M38" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="N38" s="60"/>
-      <c r="O38" s="34">
-        <v>4.2171731523020446</v>
-      </c>
-      <c r="P38" s="35">
-        <v>4.6702984752282681</v>
-      </c>
-      <c r="Q38" s="35">
-        <v>5.0608860361047316</v>
-      </c>
-      <c r="R38" s="35">
-        <v>5.9068575059271318</v>
-      </c>
-      <c r="S38" s="35">
-        <v>8.5966909141817851</v>
-      </c>
-      <c r="T38" s="35">
-        <v>10.771320326074211</v>
-      </c>
-      <c r="U38" s="36">
-        <v>10.23603152809228</v>
+      <c r="N38" s="66"/>
+      <c r="O38" s="87">
+        <v>4.3743918396131134</v>
+      </c>
+      <c r="P38" s="88">
+        <v>5.1779143655465321</v>
+      </c>
+      <c r="Q38" s="88">
+        <v>4.8362705721377752</v>
+      </c>
+      <c r="R38" s="88">
+        <v>5.6797782301447892</v>
+      </c>
+      <c r="S38" s="88">
+        <v>9.0190902977959446</v>
+      </c>
+      <c r="T38" s="88">
+        <v>11.000258135261941</v>
+      </c>
+      <c r="U38" s="89">
+        <v>9.2918474149187738</v>
       </c>
       <c r="V38" s="1" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    4.21717315230204, 4.67029847522827, 5.06088603610473, 5.90685750592713, 8.59669091418179, 10.7713203260742, 10.2360315280923,</v>
+        <v xml:space="preserve">    4.37439183961311, 5.17791436554653, 4.83627057213778, 5.67977823014479, 9.01909029779594, 11.0002581352619, 9.29184741491877,</v>
       </c>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="59" t="s">
+      <c r="A39" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="B39" s="60"/>
-      <c r="C39" s="52">
-        <v>92.570176373736686</v>
-      </c>
-      <c r="D39" s="53">
-        <v>91.035116753825534</v>
-      </c>
-      <c r="E39" s="53">
-        <v>89.995984735900805</v>
-      </c>
-      <c r="F39" s="53">
-        <v>86.101239818995751</v>
-      </c>
-      <c r="G39" s="53">
-        <v>77.099560389949318</v>
-      </c>
-      <c r="H39" s="53">
-        <v>57.996429145301242</v>
-      </c>
-      <c r="I39" s="54">
-        <v>44.399943110932981</v>
+      <c r="B39" s="66"/>
+      <c r="C39" s="87">
+        <v>92.492055194421354</v>
+      </c>
+      <c r="D39" s="88">
+        <v>91.055738083245984</v>
+      </c>
+      <c r="E39" s="88">
+        <v>89.241264887762341</v>
+      </c>
+      <c r="F39" s="88">
+        <v>82.713601809643421</v>
+      </c>
+      <c r="G39" s="88">
+        <v>73.133677048774885</v>
+      </c>
+      <c r="H39" s="88">
+        <v>56.229205901331248</v>
+      </c>
+      <c r="I39" s="89">
+        <v>43.695396708102962</v>
       </c>
       <c r="J39" s="50"/>
       <c r="K39" s="50"/>
       <c r="L39" s="1" t="str">
         <f t="shared" si="6"/>
-        <v xml:space="preserve">    92.5701763737367, 91.0351167538255, 89.9959847359008, 86.1012398189958, 77.0995603899493, 57.9964291453012, 44.399943110933,</v>
-      </c>
-      <c r="M39" s="59" t="s">
+        <v xml:space="preserve">    92.4920551944214, 91.055738083246, 89.2412648877623, 82.7136018096434, 73.1336770487749, 56.2292059013312, 43.695396708103,</v>
+      </c>
+      <c r="M39" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="N39" s="60"/>
-      <c r="O39" s="52">
-        <v>3.882028195540002</v>
-      </c>
-      <c r="P39" s="53">
-        <v>4.4292663319519576</v>
-      </c>
-      <c r="Q39" s="53">
-        <v>5.1354581403320241</v>
-      </c>
-      <c r="R39" s="53">
-        <v>5.8685355921558013</v>
-      </c>
-      <c r="S39" s="53">
-        <v>8.0663639251543504</v>
-      </c>
-      <c r="T39" s="53">
-        <v>9.5110854192429173</v>
-      </c>
-      <c r="U39" s="54">
-        <v>8.058131505188614</v>
+      <c r="N39" s="66"/>
+      <c r="O39" s="87">
+        <v>4.0986250609792014</v>
+      </c>
+      <c r="P39" s="88">
+        <v>4.5926443490712341</v>
+      </c>
+      <c r="Q39" s="88">
+        <v>4.8521598807380544</v>
+      </c>
+      <c r="R39" s="88">
+        <v>5.8188919126166327</v>
+      </c>
+      <c r="S39" s="88">
+        <v>9.5088987825376563</v>
+      </c>
+      <c r="T39" s="88">
+        <v>11.32839542788332</v>
+      </c>
+      <c r="U39" s="89">
+        <v>10.62887090695313</v>
       </c>
       <c r="V39" s="1" t="str">
         <f t="shared" si="4"/>
-        <v xml:space="preserve">    3.88202819554, 4.42926633195196, 5.13545814033202, 5.8685355921558, 8.06636392515435, 9.51108541924292, 8.05813150518861,</v>
+        <v xml:space="preserve">    4.0986250609792, 4.59264434907123, 4.85215988073805, 5.81889191261663, 9.50889878253766, 11.3283954278833, 10.6288709069531,</v>
       </c>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="60"/>
-      <c r="C40" s="34">
-        <v>92.515649858336417</v>
-      </c>
-      <c r="D40" s="35">
-        <v>90.633837177608882</v>
-      </c>
-      <c r="E40" s="35">
-        <v>89.218749027706451</v>
-      </c>
-      <c r="F40" s="35">
-        <v>83.159104859904048</v>
-      </c>
-      <c r="G40" s="35">
-        <v>75.205406346603183</v>
-      </c>
-      <c r="H40" s="35">
-        <v>58.328595951322271</v>
-      </c>
-      <c r="I40" s="36">
-        <v>44.663256049071087</v>
+      <c r="B40" s="66"/>
+      <c r="C40" s="90">
+        <v>92.657174075741665</v>
+      </c>
+      <c r="D40" s="91">
+        <v>91.208050814372243</v>
+      </c>
+      <c r="E40" s="91">
+        <v>89.170455678091372</v>
+      </c>
+      <c r="F40" s="91">
+        <v>84.474616062770011</v>
+      </c>
+      <c r="G40" s="91">
+        <v>75.066668593640316</v>
+      </c>
+      <c r="H40" s="91">
+        <v>58.520340993368222</v>
+      </c>
+      <c r="I40" s="92">
+        <v>44.786141592049418</v>
       </c>
       <c r="J40" s="58"/>
       <c r="K40" s="58"/>
       <c r="L40" s="57"/>
-      <c r="M40" s="59" t="s">
+      <c r="M40" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="N40" s="60"/>
-      <c r="O40" s="34">
-        <v>4.2818937520906779</v>
-      </c>
-      <c r="P40" s="35">
-        <v>5.0215820890726173</v>
-      </c>
-      <c r="Q40" s="35">
-        <v>5.2048209810817641</v>
-      </c>
-      <c r="R40" s="35">
-        <v>6.0125954692045056</v>
-      </c>
-      <c r="S40" s="35">
-        <v>8.4472284006849367</v>
-      </c>
-      <c r="T40" s="35">
-        <v>11.323085110814951</v>
-      </c>
-      <c r="U40" s="36">
-        <v>10.33126321411414</v>
+      <c r="N40" s="66"/>
+      <c r="O40" s="90">
+        <v>4.2589004392769629</v>
+      </c>
+      <c r="P40" s="91">
+        <v>4.8517186601265534</v>
+      </c>
+      <c r="Q40" s="91">
+        <v>5.6717673083496472</v>
+      </c>
+      <c r="R40" s="91">
+        <v>5.3079507961921779</v>
+      </c>
+      <c r="S40" s="91">
+        <v>7.7884705615072454</v>
+      </c>
+      <c r="T40" s="91">
+        <v>10.595563377926201</v>
+      </c>
+      <c r="U40" s="92">
+        <v>10.945843294214329</v>
       </c>
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="59" t="s">
+      <c r="A41" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="B41" s="63"/>
-      <c r="C41" s="64"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="62"/>
+      <c r="B41" s="67"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="71"/>
+      <c r="G41" s="71"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="72"/>
       <c r="J41" s="50"/>
       <c r="K41" s="50"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="59" t="s">
+      <c r="M41" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="N41" s="63"/>
-      <c r="O41" s="64"/>
-      <c r="P41" s="64"/>
-      <c r="Q41" s="64"/>
-      <c r="R41" s="64"/>
-      <c r="S41" s="64"/>
-      <c r="T41" s="64"/>
-      <c r="U41" s="62"/>
+      <c r="N41" s="67"/>
+      <c r="O41" s="71"/>
+      <c r="P41" s="71"/>
+      <c r="Q41" s="71"/>
+      <c r="R41" s="71"/>
+      <c r="S41" s="71"/>
+      <c r="T41" s="71"/>
+      <c r="U41" s="72"/>
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="59" t="s">
+      <c r="A42" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="B42" s="60"/>
-      <c r="C42" s="34">
-        <v>91.365503103283018</v>
-      </c>
-      <c r="D42" s="35">
-        <v>90.485891056064375</v>
-      </c>
-      <c r="E42" s="35">
-        <v>89.568582528718636</v>
-      </c>
-      <c r="F42" s="35">
-        <v>87.35503422782692</v>
-      </c>
-      <c r="G42" s="35">
-        <v>83.775802183320806</v>
-      </c>
-      <c r="H42" s="35">
-        <v>59.664242373274107</v>
-      </c>
-      <c r="I42" s="36">
-        <v>38.734493305012087</v>
+      <c r="B42" s="66"/>
+      <c r="C42" s="84">
+        <v>92.603769819293618</v>
+      </c>
+      <c r="D42" s="85">
+        <v>91.431947068352812</v>
+      </c>
+      <c r="E42" s="85">
+        <v>90.390795042999585</v>
+      </c>
+      <c r="F42" s="85">
+        <v>86.789562828222273</v>
+      </c>
+      <c r="G42" s="85">
+        <v>80.615554033052248</v>
+      </c>
+      <c r="H42" s="85">
+        <v>56.609578553133908</v>
+      </c>
+      <c r="I42" s="86">
+        <v>41.27928062292434</v>
       </c>
       <c r="J42" s="50"/>
       <c r="K42" s="50"/>
       <c r="L42" s="1" t="str">
         <f t="shared" ref="L42:L44" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C42:I42)&amp;","</f>
-        <v xml:space="preserve">    91.365503103283, 90.4858910560644, 89.5685825287186, 87.3550342278269, 83.7758021833208, 59.6642423732741, 38.7344933050121,</v>
-      </c>
-      <c r="M42" s="59" t="s">
+        <v xml:space="preserve">    92.6037698192936, 91.4319470683528, 90.3907950429996, 86.7895628282223, 80.6155540330522, 56.6095785531339, 41.2792806229243,</v>
+      </c>
+      <c r="M42" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="N42" s="60"/>
-      <c r="O42" s="34">
-        <v>3.8096312747348571</v>
-      </c>
-      <c r="P42" s="35">
-        <v>3.3823322749479061</v>
-      </c>
-      <c r="Q42" s="35">
-        <v>3.1901414384399041</v>
-      </c>
-      <c r="R42" s="35">
-        <v>3.435608860758363</v>
-      </c>
-      <c r="S42" s="35">
-        <v>3.9801135842717961</v>
-      </c>
-      <c r="T42" s="35">
-        <v>7.4065519031840097</v>
-      </c>
-      <c r="U42" s="36">
-        <v>4.3412957141341879</v>
+      <c r="N42" s="66"/>
+      <c r="O42" s="84">
+        <v>3.708759274801273</v>
+      </c>
+      <c r="P42" s="85">
+        <v>3.9640390541215931</v>
+      </c>
+      <c r="Q42" s="85">
+        <v>3.7067998106756881</v>
+      </c>
+      <c r="R42" s="85">
+        <v>3.667452632531309</v>
+      </c>
+      <c r="S42" s="85">
+        <v>5.7548227051500218</v>
+      </c>
+      <c r="T42" s="85">
+        <v>8.5366536877555248</v>
+      </c>
+      <c r="U42" s="86">
+        <v>6.3187793027043018</v>
       </c>
       <c r="V42" s="1" t="str">
         <f t="shared" ref="V42:V44" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O42:U42)&amp;","</f>
-        <v xml:space="preserve">    3.80963127473486, 3.38233227494791, 3.1901414384399, 3.43560886075836, 3.9801135842718, 7.40655190318401, 4.34129571413419,</v>
+        <v xml:space="preserve">    3.70875927480127, 3.96403905412159, 3.70679981067569, 3.66745263253131, 5.75482270515002, 8.53665368775552, 6.3187793027043,</v>
       </c>
     </row>
     <row r="43" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="61" t="s">
+      <c r="A43" s="70" t="s">
         <v>8</v>
       </c>
-      <c r="B43" s="62"/>
-      <c r="C43" s="34">
-        <v>91.352017689458577</v>
-      </c>
-      <c r="D43" s="35">
-        <v>90.612646908845178</v>
-      </c>
-      <c r="E43" s="35">
-        <v>89.673109045448143</v>
-      </c>
-      <c r="F43" s="35">
-        <v>87.570648852891097</v>
-      </c>
-      <c r="G43" s="35">
-        <v>85.153610116106222</v>
-      </c>
-      <c r="H43" s="35">
-        <v>70.154101376724071</v>
-      </c>
-      <c r="I43" s="36">
-        <v>44.255354014211143</v>
+      <c r="B43" s="69"/>
+      <c r="C43" s="87">
+        <v>91.377634404932721</v>
+      </c>
+      <c r="D43" s="88">
+        <v>90.405373333245066</v>
+      </c>
+      <c r="E43" s="88">
+        <v>89.371480308332721</v>
+      </c>
+      <c r="F43" s="88">
+        <v>87.60989862639515</v>
+      </c>
+      <c r="G43" s="88">
+        <v>85.537230701510694</v>
+      </c>
+      <c r="H43" s="88">
+        <v>70.930708745421484</v>
+      </c>
+      <c r="I43" s="89">
+        <v>44.097326232806537</v>
       </c>
       <c r="J43" s="50"/>
       <c r="K43" s="50"/>
       <c r="L43" s="1" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    91.3520176894586, 90.6126469088452, 89.6731090454481, 87.5706488528911, 85.1536101161062, 70.1541013767241, 44.2553540142111,</v>
-      </c>
-      <c r="M43" s="59" t="s">
+        <v xml:space="preserve">    91.3776344049327, 90.4053733332451, 89.3714803083327, 87.6098986263952, 85.5372307015107, 70.9307087454215, 44.0973262328065,</v>
+      </c>
+      <c r="M43" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="N43" s="60"/>
-      <c r="O43" s="34">
-        <v>3.6410788132464011</v>
-      </c>
-      <c r="P43" s="35">
-        <v>3.0474479281352909</v>
-      </c>
-      <c r="Q43" s="35">
-        <v>2.5295084567057469</v>
-      </c>
-      <c r="R43" s="35">
-        <v>2.7268738132327659</v>
-      </c>
-      <c r="S43" s="35">
-        <v>4.0335194528578784</v>
-      </c>
-      <c r="T43" s="35">
-        <v>5.245193605897664</v>
-      </c>
-      <c r="U43" s="36">
-        <v>2.5110804834384211</v>
+      <c r="N43" s="66"/>
+      <c r="O43" s="87">
+        <v>3.5684194304484111</v>
+      </c>
+      <c r="P43" s="88">
+        <v>3.0347581440341318</v>
+      </c>
+      <c r="Q43" s="88">
+        <v>2.754130276526872</v>
+      </c>
+      <c r="R43" s="88">
+        <v>2.7768782002466339</v>
+      </c>
+      <c r="S43" s="88">
+        <v>3.3184641894178428</v>
+      </c>
+      <c r="T43" s="88">
+        <v>4.9795199020249923</v>
+      </c>
+      <c r="U43" s="89">
+        <v>2.9223071611371929</v>
       </c>
       <c r="V43" s="1" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    3.6410788132464, 3.04744792813529, 2.52950845670575, 2.72687381323277, 4.03351945285788, 5.24519360589766, 2.51108048343842,</v>
+        <v xml:space="preserve">    3.56841943044841, 3.03475814403413, 2.75413027652687, 2.77687820024663, 3.31846418941784, 4.97951990202499, 2.92230716113719,</v>
       </c>
     </row>
     <row r="44" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="59" t="s">
+      <c r="A44" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="B44" s="60"/>
-      <c r="C44" s="34">
-        <v>92.61946302134767</v>
-      </c>
-      <c r="D44" s="35">
-        <v>91.641845498508658</v>
-      </c>
-      <c r="E44" s="35">
-        <v>90.604490520989373</v>
-      </c>
-      <c r="F44" s="35">
-        <v>86.028930620603035</v>
-      </c>
-      <c r="G44" s="35">
-        <v>77.869547765340229</v>
-      </c>
-      <c r="H44" s="35">
-        <v>58.066616072179237</v>
-      </c>
-      <c r="I44" s="36">
-        <v>44.282072681774139</v>
+      <c r="B44" s="66"/>
+      <c r="C44" s="87">
+        <v>92.603715202692385</v>
+      </c>
+      <c r="D44" s="88">
+        <v>91.484997502720319</v>
+      </c>
+      <c r="E44" s="88">
+        <v>90.630171299324857</v>
+      </c>
+      <c r="F44" s="88">
+        <v>85.342034697064548</v>
+      </c>
+      <c r="G44" s="88">
+        <v>78.208607944308184</v>
+      </c>
+      <c r="H44" s="88">
+        <v>58.188767254712552</v>
+      </c>
+      <c r="I44" s="89">
+        <v>45.468919562576168</v>
       </c>
       <c r="J44" s="50"/>
       <c r="K44" s="50"/>
       <c r="L44" s="1" t="str">
         <f t="shared" si="7"/>
-        <v xml:space="preserve">    92.6194630213477, 91.6418454985087, 90.6044905209894, 86.028930620603, 77.8695477653402, 58.0666160721792, 44.2820726817741,</v>
-      </c>
-      <c r="M44" s="59" t="s">
+        <v xml:space="preserve">    92.6037152026924, 91.4849975027203, 90.6301712993249, 85.3420346970645, 78.2086079443082, 58.1887672547126, 45.4689195625762,</v>
+      </c>
+      <c r="M44" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="N44" s="60"/>
-      <c r="O44" s="34">
-        <v>4.1202488894386304</v>
-      </c>
-      <c r="P44" s="35">
-        <v>4.4587262447220368</v>
-      </c>
-      <c r="Q44" s="35">
-        <v>4.1451701238630649</v>
-      </c>
-      <c r="R44" s="35">
-        <v>4.7547668035033421</v>
-      </c>
-      <c r="S44" s="35">
-        <v>7.3962800398529813</v>
-      </c>
-      <c r="T44" s="35">
-        <v>11.13409225199972</v>
-      </c>
-      <c r="U44" s="36">
-        <v>10.21410985821676</v>
+      <c r="N44" s="66"/>
+      <c r="O44" s="87">
+        <v>4.0727132923350373</v>
+      </c>
+      <c r="P44" s="88">
+        <v>4.4231285957629458</v>
+      </c>
+      <c r="Q44" s="88">
+        <v>4.3011534303531356</v>
+      </c>
+      <c r="R44" s="88">
+        <v>4.8453894583465429</v>
+      </c>
+      <c r="S44" s="88">
+        <v>7.5589700135942426</v>
+      </c>
+      <c r="T44" s="88">
+        <v>10.3740336621021</v>
+      </c>
+      <c r="U44" s="89">
+        <v>10.707618741543239</v>
       </c>
       <c r="V44" s="1" t="str">
         <f t="shared" si="8"/>
-        <v xml:space="preserve">    4.12024888943863, 4.45872624472204, 4.14517012386306, 4.75476680350334, 7.39628003985298, 11.1340922519997, 10.2141098582168,</v>
+        <v xml:space="preserve">    4.07271329233504, 4.42312859576295, 4.30115343035314, 4.84538945834654, 7.55897001359424, 10.3740336621021, 10.7076187415432,</v>
       </c>
     </row>
     <row r="45" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="59" t="s">
+      <c r="A45" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="B45" s="60"/>
-      <c r="C45" s="34">
-        <v>92.836313492728166</v>
-      </c>
-      <c r="D45" s="35">
-        <v>91.35902579070337</v>
-      </c>
-      <c r="E45" s="35">
-        <v>89.600386013681359</v>
-      </c>
-      <c r="F45" s="35">
-        <v>83.549429512462467</v>
-      </c>
-      <c r="G45" s="35">
-        <v>75.443451304684089</v>
-      </c>
-      <c r="H45" s="35">
-        <v>58.040988875657007</v>
-      </c>
-      <c r="I45" s="36">
-        <v>44.45694317203499</v>
+      <c r="B45" s="66"/>
+      <c r="C45" s="90">
+        <v>92.692685851985146</v>
+      </c>
+      <c r="D45" s="91">
+        <v>91.028008929063319</v>
+      </c>
+      <c r="E45" s="91">
+        <v>89.101176850288709</v>
+      </c>
+      <c r="F45" s="91">
+        <v>84.121695311135312</v>
+      </c>
+      <c r="G45" s="91">
+        <v>75.514536359946376</v>
+      </c>
+      <c r="H45" s="91">
+        <v>58.551851548300363</v>
+      </c>
+      <c r="I45" s="92">
+        <v>43.528644478603361</v>
       </c>
       <c r="J45" s="50"/>
       <c r="K45" s="50"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="59" t="s">
+      <c r="M45" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="N45" s="60"/>
-      <c r="O45" s="34">
-        <v>4.0350169218649814</v>
-      </c>
-      <c r="P45" s="35">
-        <v>4.8715238888136483</v>
-      </c>
-      <c r="Q45" s="35">
-        <v>5.0114819755482234</v>
-      </c>
-      <c r="R45" s="35">
-        <v>5.5418311462698613</v>
-      </c>
-      <c r="S45" s="35">
-        <v>8.7209269933539382</v>
-      </c>
-      <c r="T45" s="35">
-        <v>10.65690967583773</v>
-      </c>
-      <c r="U45" s="36">
-        <v>11.553116561579911</v>
+      <c r="N45" s="66"/>
+      <c r="O45" s="90">
+        <v>4.3508377678439567</v>
+      </c>
+      <c r="P45" s="91">
+        <v>5.1455197984597092</v>
+      </c>
+      <c r="Q45" s="91">
+        <v>5.0319449257944937</v>
+      </c>
+      <c r="R45" s="91">
+        <v>5.4881092234662896</v>
+      </c>
+      <c r="S45" s="91">
+        <v>8.3963724907401343</v>
+      </c>
+      <c r="T45" s="91">
+        <v>11.26477476806841</v>
+      </c>
+      <c r="U45" s="92">
+        <v>10.478269846537319</v>
       </c>
       <c r="V45" s="1"/>
     </row>
@@ -5871,17 +5955,32 @@
     </row>
   </sheetData>
   <mergeCells count="56">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="M44:N44"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="M45:N45"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="M41:U41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="M42:N42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="M43:N43"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="M13:U13"/>
+    <mergeCell ref="M36:U36"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="M28:U28"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
     <mergeCell ref="A39:B39"/>
     <mergeCell ref="A40:B40"/>
     <mergeCell ref="M39:N39"/>
@@ -5898,35 +5997,20 @@
     <mergeCell ref="M27:N27"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A36:I36"/>
-    <mergeCell ref="M13:U13"/>
-    <mergeCell ref="M36:U36"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:I5"/>
     <mergeCell ref="M5:U5"/>
-    <mergeCell ref="M28:U28"/>
-    <mergeCell ref="A18:I18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
     <mergeCell ref="M18:U18"/>
     <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="M44:N44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="M45:N45"/>
-    <mergeCell ref="A41:I41"/>
-    <mergeCell ref="M41:U41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="M42:N42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="M43:N43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C14:I16 C6:I7 C2:I4 C10:I12">

--- a/results_cnn_subnetwork_evaluation/summary.xlsx
+++ b/results_cnn_subnetwork_evaluation/summary.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AFB12DF-A583-4AEC-AD58-C902FC721171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="partialdata_20260407" sheetId="6" r:id="rId1"/>
